--- a/Hoadon/HD2026/HDVao/9/3502550210_HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HD2026/HDVao/9/3502550210_HDDienTuMayTinhTien.xlsx
@@ -1701,32 +1701,32 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>C26MMM</t>
+          <t>C26MYY</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>133</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>079056002409</t>
+          <t>077196000132</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>Cường Hưng</t>
+          <t>Nguyễn Thị Minh Tuyền</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>390i, Nguyễn Duy, Phường Chánh Hưng, Hồ Chí Minh, Việt Nam</t>
+          <t>441/6/4 đường Trần Phú, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr">
@@ -1746,7 +1746,7 @@
         <v>0.0</v>
       </c>
       <c r="O27" s="13" t="n">
-        <v>3400000.0</v>
+        <v>3575000.0</v>
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
@@ -1775,12 +1775,12 @@
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>106</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
@@ -1839,32 +1839,32 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>C26MMH</t>
+          <t>C26MMM</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>114</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>079078009688</t>
+          <t>079056002409</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH MẠNH HIẾU</t>
+          <t>Cường Hưng</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>606 Tân Kỳ Tân Quý, KP7, P.Bình Hưng Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>390i, Nguyễn Duy, Phường Chánh Hưng, Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I29" s="7" t="inlineStr">
@@ -1880,9 +1880,11 @@
       <c r="K29" s="6"/>
       <c r="L29" s="13"/>
       <c r="M29" s="13"/>
-      <c r="N29" s="13"/>
+      <c r="N29" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="O29" s="13" t="n">
-        <v>3700000.0</v>
+        <v>3400000.0</v>
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
@@ -1901,37 +1903,37 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>C26MRV</t>
+          <t>C26MMH</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>46147</t>
+          <t>320</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>3500704465</t>
+          <t>079078009688</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+          <t>HỘ KINH DOANH MẠNH HIẾU</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>606 Tân Kỳ Tân Quý, KP7, P.Bình Hưng Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
@@ -1945,17 +1947,11 @@
         </is>
       </c>
       <c r="K30" s="6"/>
-      <c r="L30" s="13" t="n">
-        <v>9220370.0</v>
-      </c>
-      <c r="M30" s="13" t="n">
-        <v>737630.0</v>
-      </c>
-      <c r="N30" s="13" t="n">
-        <v>484030.0</v>
-      </c>
+      <c r="L30" s="13"/>
+      <c r="M30" s="13"/>
+      <c r="N30" s="13"/>
       <c r="O30" s="13" t="n">
-        <v>9958000.0</v>
+        <v>3700000.0</v>
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
@@ -1984,7 +1980,7 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>46241</t>
+          <t>46147</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
@@ -2019,16 +2015,16 @@
       </c>
       <c r="K31" s="6"/>
       <c r="L31" s="13" t="n">
-        <v>1667270.0</v>
+        <v>9220370.0</v>
       </c>
       <c r="M31" s="13" t="n">
-        <v>133382.0</v>
+        <v>737630.0</v>
       </c>
       <c r="N31" s="13" t="n">
-        <v>0.0</v>
+        <v>484030.0</v>
       </c>
       <c r="O31" s="13" t="n">
-        <v>1800652.0</v>
+        <v>9958000.0</v>
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
@@ -2057,12 +2053,12 @@
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>46293</t>
+          <t>46241</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
@@ -2092,16 +2088,16 @@
       </c>
       <c r="K32" s="6"/>
       <c r="L32" s="13" t="n">
-        <v>3740741.0</v>
+        <v>1667270.0</v>
       </c>
       <c r="M32" s="13" t="n">
-        <v>299259.0</v>
+        <v>133382.0</v>
       </c>
       <c r="N32" s="13" t="n">
-        <v>501259.0</v>
+        <v>0.0</v>
       </c>
       <c r="O32" s="13" t="n">
-        <v>4040000.0</v>
+        <v>1800652.0</v>
       </c>
       <c r="P32" s="6" t="inlineStr">
         <is>
@@ -2130,12 +2126,12 @@
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>46700</t>
+          <t>46293</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
@@ -2165,16 +2161,16 @@
       </c>
       <c r="K33" s="6"/>
       <c r="L33" s="13" t="n">
-        <v>5728120.0</v>
+        <v>3740741.0</v>
       </c>
       <c r="M33" s="13" t="n">
-        <v>458250.0</v>
+        <v>299259.0</v>
       </c>
       <c r="N33" s="13" t="n">
-        <v>0.0</v>
+        <v>501259.0</v>
       </c>
       <c r="O33" s="13" t="n">
-        <v>6186370.0</v>
+        <v>4040000.0</v>
       </c>
       <c r="P33" s="6" t="inlineStr">
         <is>
@@ -2203,7 +2199,7 @@
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>46701</t>
+          <t>46700</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
@@ -2238,16 +2234,16 @@
       </c>
       <c r="K34" s="6"/>
       <c r="L34" s="13" t="n">
-        <v>1321200.0</v>
+        <v>5728120.0</v>
       </c>
       <c r="M34" s="13" t="n">
-        <v>105696.0</v>
+        <v>458250.0</v>
       </c>
       <c r="N34" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O34" s="13" t="n">
-        <v>1426896.0</v>
+        <v>6186370.0</v>
       </c>
       <c r="P34" s="6" t="inlineStr">
         <is>
@@ -2276,7 +2272,7 @@
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>46725</t>
+          <t>46701</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
@@ -2311,16 +2307,16 @@
       </c>
       <c r="K35" s="6"/>
       <c r="L35" s="13" t="n">
-        <v>3588000.0</v>
+        <v>1321200.0</v>
       </c>
       <c r="M35" s="13" t="n">
-        <v>287040.0</v>
+        <v>105696.0</v>
       </c>
       <c r="N35" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O35" s="13" t="n">
-        <v>3875040.0</v>
+        <v>1426896.0</v>
       </c>
       <c r="P35" s="6" t="inlineStr">
         <is>
@@ -2349,12 +2345,12 @@
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>47160</t>
+          <t>46725</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
@@ -2384,16 +2380,16 @@
       </c>
       <c r="K36" s="6"/>
       <c r="L36" s="13" t="n">
-        <v>2566442.0</v>
+        <v>3588000.0</v>
       </c>
       <c r="M36" s="13" t="n">
-        <v>205315.0</v>
+        <v>287040.0</v>
       </c>
       <c r="N36" s="13" t="n">
-        <v>28158.0</v>
+        <v>0.0</v>
       </c>
       <c r="O36" s="13" t="n">
-        <v>2771757.0</v>
+        <v>3875040.0</v>
       </c>
       <c r="P36" s="6" t="inlineStr">
         <is>
@@ -2422,7 +2418,7 @@
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>47161</t>
+          <t>47160</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
@@ -2457,16 +2453,16 @@
       </c>
       <c r="K37" s="6"/>
       <c r="L37" s="13" t="n">
-        <v>2527200.0</v>
+        <v>2566442.0</v>
       </c>
       <c r="M37" s="13" t="n">
-        <v>202176.0</v>
+        <v>205315.0</v>
       </c>
       <c r="N37" s="13" t="n">
-        <v>0.0</v>
+        <v>28158.0</v>
       </c>
       <c r="O37" s="13" t="n">
-        <v>2729376.0</v>
+        <v>2771757.0</v>
       </c>
       <c r="P37" s="6" t="inlineStr">
         <is>
@@ -2495,12 +2491,12 @@
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>47417</t>
+          <t>47161</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
@@ -2530,16 +2526,16 @@
       </c>
       <c r="K38" s="6"/>
       <c r="L38" s="13" t="n">
-        <v>2214900.0</v>
+        <v>2527200.0</v>
       </c>
       <c r="M38" s="13" t="n">
-        <v>177192.0</v>
+        <v>202176.0</v>
       </c>
       <c r="N38" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O38" s="13" t="n">
-        <v>2392092.0</v>
+        <v>2729376.0</v>
       </c>
       <c r="P38" s="6" t="inlineStr">
         <is>
@@ -2568,12 +2564,12 @@
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>47657</t>
+          <t>47417</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
@@ -2603,16 +2599,16 @@
       </c>
       <c r="K39" s="6"/>
       <c r="L39" s="13" t="n">
-        <v>2512226.0</v>
+        <v>2214900.0</v>
       </c>
       <c r="M39" s="13" t="n">
-        <v>200978.0</v>
+        <v>177192.0</v>
       </c>
       <c r="N39" s="13" t="n">
-        <v>124874.0</v>
+        <v>0.0</v>
       </c>
       <c r="O39" s="13" t="n">
-        <v>2713204.0</v>
+        <v>2392092.0</v>
       </c>
       <c r="P39" s="6" t="inlineStr">
         <is>
@@ -2641,7 +2637,7 @@
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>47674</t>
+          <t>47657</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
@@ -2676,16 +2672,16 @@
       </c>
       <c r="K40" s="6"/>
       <c r="L40" s="13" t="n">
-        <v>3304000.0</v>
+        <v>2512226.0</v>
       </c>
       <c r="M40" s="13" t="n">
-        <v>264320.0</v>
+        <v>200978.0</v>
       </c>
       <c r="N40" s="13" t="n">
-        <v>0.0</v>
+        <v>124874.0</v>
       </c>
       <c r="O40" s="13" t="n">
-        <v>3568320.0</v>
+        <v>2713204.0</v>
       </c>
       <c r="P40" s="6" t="inlineStr">
         <is>
@@ -2714,12 +2710,12 @@
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>47747</t>
+          <t>47674</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
@@ -2749,16 +2745,16 @@
       </c>
       <c r="K41" s="6"/>
       <c r="L41" s="13" t="n">
-        <v>3.8462963E7</v>
+        <v>3304000.0</v>
       </c>
       <c r="M41" s="13" t="n">
-        <v>3077037.0</v>
+        <v>264320.0</v>
       </c>
       <c r="N41" s="13" t="n">
-        <v>2559037.0</v>
+        <v>0.0</v>
       </c>
       <c r="O41" s="13" t="n">
-        <v>4.154E7</v>
+        <v>3568320.0</v>
       </c>
       <c r="P41" s="6" t="inlineStr">
         <is>
@@ -2787,12 +2783,12 @@
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>48032</t>
+          <t>47747</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
@@ -2822,16 +2818,16 @@
       </c>
       <c r="K42" s="6"/>
       <c r="L42" s="13" t="n">
-        <v>2982590.0</v>
+        <v>3.8462963E7</v>
       </c>
       <c r="M42" s="13" t="n">
-        <v>238607.0</v>
+        <v>3077037.0</v>
       </c>
       <c r="N42" s="13" t="n">
-        <v>0.0</v>
+        <v>2559037.0</v>
       </c>
       <c r="O42" s="13" t="n">
-        <v>3221197.0</v>
+        <v>4.154E7</v>
       </c>
       <c r="P42" s="6" t="inlineStr">
         <is>
@@ -2860,12 +2856,12 @@
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>48441</t>
+          <t>48032</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
@@ -2895,16 +2891,16 @@
       </c>
       <c r="K43" s="6"/>
       <c r="L43" s="13" t="n">
-        <v>4676000.0</v>
+        <v>2982590.0</v>
       </c>
       <c r="M43" s="13" t="n">
-        <v>374080.0</v>
+        <v>238607.0</v>
       </c>
       <c r="N43" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O43" s="13" t="n">
-        <v>5050080.0</v>
+        <v>3221197.0</v>
       </c>
       <c r="P43" s="6" t="inlineStr">
         <is>
@@ -2933,7 +2929,7 @@
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>48442</t>
+          <t>48441</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
@@ -2968,16 +2964,16 @@
       </c>
       <c r="K44" s="6"/>
       <c r="L44" s="13" t="n">
-        <v>5013650.0</v>
+        <v>4676000.0</v>
       </c>
       <c r="M44" s="13" t="n">
-        <v>401092.0</v>
+        <v>374080.0</v>
       </c>
       <c r="N44" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O44" s="13" t="n">
-        <v>5414742.0</v>
+        <v>5050080.0</v>
       </c>
       <c r="P44" s="6" t="inlineStr">
         <is>
@@ -3006,12 +3002,12 @@
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>48834</t>
+          <t>48442</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
@@ -3041,16 +3037,16 @@
       </c>
       <c r="K45" s="6"/>
       <c r="L45" s="13" t="n">
-        <v>2238242.0</v>
+        <v>5013650.0</v>
       </c>
       <c r="M45" s="13" t="n">
-        <v>179059.0</v>
+        <v>401092.0</v>
       </c>
       <c r="N45" s="13" t="n">
-        <v>28158.0</v>
+        <v>0.0</v>
       </c>
       <c r="O45" s="13" t="n">
-        <v>2417301.0</v>
+        <v>5414742.0</v>
       </c>
       <c r="P45" s="6" t="inlineStr">
         <is>
@@ -3079,12 +3075,12 @@
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>49247</t>
+          <t>48834</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
@@ -3114,16 +3110,16 @@
       </c>
       <c r="K46" s="6"/>
       <c r="L46" s="13" t="n">
-        <v>2208000.0</v>
+        <v>2238242.0</v>
       </c>
       <c r="M46" s="13" t="n">
-        <v>176640.0</v>
+        <v>179059.0</v>
       </c>
       <c r="N46" s="13" t="n">
-        <v>0.0</v>
+        <v>28158.0</v>
       </c>
       <c r="O46" s="13" t="n">
-        <v>2384640.0</v>
+        <v>2417301.0</v>
       </c>
       <c r="P46" s="6" t="inlineStr">
         <is>
@@ -3152,12 +3148,12 @@
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>49424</t>
+          <t>49247</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
@@ -3187,16 +3183,16 @@
       </c>
       <c r="K47" s="6"/>
       <c r="L47" s="13" t="n">
-        <v>4488889.0</v>
+        <v>2208000.0</v>
       </c>
       <c r="M47" s="13" t="n">
-        <v>359111.0</v>
+        <v>176640.0</v>
       </c>
       <c r="N47" s="13" t="n">
-        <v>601511.0</v>
+        <v>0.0</v>
       </c>
       <c r="O47" s="13" t="n">
-        <v>4848000.0</v>
+        <v>2384640.0</v>
       </c>
       <c r="P47" s="6" t="inlineStr">
         <is>
@@ -3225,7 +3221,7 @@
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>49427</t>
+          <t>49424</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
@@ -3260,16 +3256,16 @@
       </c>
       <c r="K48" s="6"/>
       <c r="L48" s="13" t="n">
-        <v>0.0</v>
+        <v>4488889.0</v>
       </c>
       <c r="M48" s="13" t="n">
-        <v>0.0</v>
+        <v>359111.0</v>
       </c>
       <c r="N48" s="13" t="n">
-        <v>0.0</v>
+        <v>601511.0</v>
       </c>
       <c r="O48" s="13" t="n">
-        <v>0.0</v>
+        <v>4848000.0</v>
       </c>
       <c r="P48" s="6" t="inlineStr">
         <is>
@@ -3298,7 +3294,7 @@
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>49491</t>
+          <t>49427</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
@@ -3333,16 +3329,16 @@
       </c>
       <c r="K49" s="6"/>
       <c r="L49" s="13" t="n">
-        <v>660700.0</v>
+        <v>0.0</v>
       </c>
       <c r="M49" s="13" t="n">
-        <v>52856.0</v>
+        <v>0.0</v>
       </c>
       <c r="N49" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O49" s="13" t="n">
-        <v>713556.0</v>
+        <v>0.0</v>
       </c>
       <c r="P49" s="6" t="inlineStr">
         <is>
@@ -3371,7 +3367,7 @@
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>49492</t>
+          <t>49491</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
@@ -3406,16 +3402,16 @@
       </c>
       <c r="K50" s="6"/>
       <c r="L50" s="13" t="n">
-        <v>1800739.0</v>
+        <v>660700.0</v>
       </c>
       <c r="M50" s="13" t="n">
-        <v>144059.0</v>
+        <v>52856.0</v>
       </c>
       <c r="N50" s="13" t="n">
-        <v>83761.0</v>
+        <v>0.0</v>
       </c>
       <c r="O50" s="13" t="n">
-        <v>1944798.0</v>
+        <v>713556.0</v>
       </c>
       <c r="P50" s="6" t="inlineStr">
         <is>
@@ -3444,12 +3440,12 @@
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>49563</t>
+          <t>49492</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
@@ -3479,16 +3475,16 @@
       </c>
       <c r="K51" s="6"/>
       <c r="L51" s="13" t="n">
-        <v>959044.0</v>
+        <v>1800739.0</v>
       </c>
       <c r="M51" s="13" t="n">
-        <v>76724.0</v>
+        <v>144059.0</v>
       </c>
       <c r="N51" s="13" t="n">
-        <v>106556.0</v>
+        <v>83761.0</v>
       </c>
       <c r="O51" s="13" t="n">
-        <v>1035768.0</v>
+        <v>1944798.0</v>
       </c>
       <c r="P51" s="6" t="inlineStr">
         <is>
@@ -3517,7 +3513,7 @@
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>49664</t>
+          <t>49563</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
@@ -3552,16 +3548,16 @@
       </c>
       <c r="K52" s="6"/>
       <c r="L52" s="13" t="n">
-        <v>5654100.0</v>
+        <v>959044.0</v>
       </c>
       <c r="M52" s="13" t="n">
-        <v>452328.0</v>
+        <v>76724.0</v>
       </c>
       <c r="N52" s="13" t="n">
-        <v>0.0</v>
+        <v>106556.0</v>
       </c>
       <c r="O52" s="13" t="n">
-        <v>6106428.0</v>
+        <v>1035768.0</v>
       </c>
       <c r="P52" s="6" t="inlineStr">
         <is>
@@ -3590,7 +3586,7 @@
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>49665</t>
+          <t>49664</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
@@ -3625,16 +3621,16 @@
       </c>
       <c r="K53" s="6"/>
       <c r="L53" s="13" t="n">
-        <v>1476000.0</v>
+        <v>5654100.0</v>
       </c>
       <c r="M53" s="13" t="n">
-        <v>118080.0</v>
+        <v>452328.0</v>
       </c>
       <c r="N53" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O53" s="13" t="n">
-        <v>1594080.0</v>
+        <v>6106428.0</v>
       </c>
       <c r="P53" s="6" t="inlineStr">
         <is>
@@ -3658,32 +3654,32 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>C26MRT</t>
+          <t>C26MRV</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>19674</t>
+          <t>49665</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>3501013206</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI BẠCH MAI</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H54" s="6" t="inlineStr">
         <is>
-          <t>Số 01A Tô Nguyệt Đình, Phường Long Hương, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I54" s="7" t="inlineStr">
@@ -3698,16 +3694,16 @@
       </c>
       <c r="K54" s="6"/>
       <c r="L54" s="13" t="n">
-        <v>3944445.0</v>
+        <v>1476000.0</v>
       </c>
       <c r="M54" s="13" t="n">
-        <v>315555.0</v>
+        <v>118080.0</v>
       </c>
       <c r="N54" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O54" s="13" t="n">
-        <v>4260000.0</v>
+        <v>1594080.0</v>
       </c>
       <c r="P54" s="6" t="inlineStr">
         <is>
@@ -3731,32 +3727,32 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>C26MRT</t>
+          <t>C26MRV</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>19874</t>
+          <t>49891</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>3501013206</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI BẠCH MAI</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H55" s="6" t="inlineStr">
         <is>
-          <t>Số 01A Tô Nguyệt Đình, Phường Long Hương, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I55" s="7" t="inlineStr">
@@ -3771,16 +3767,16 @@
       </c>
       <c r="K55" s="6"/>
       <c r="L55" s="13" t="n">
-        <v>2425926.0</v>
+        <v>5040220.0</v>
       </c>
       <c r="M55" s="13" t="n">
-        <v>194074.0</v>
+        <v>403218.0</v>
       </c>
       <c r="N55" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O55" s="13" t="n">
-        <v>2620000.0</v>
+        <v>5443438.0</v>
       </c>
       <c r="P55" s="6" t="inlineStr">
         <is>
@@ -3804,32 +3800,32 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>C26MHD</t>
+          <t>C26MRV</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50131</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>3501663719</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HẢI ĐOÀN</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>Số 135 đường 2/9, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I56" s="7" t="inlineStr">
@@ -3844,16 +3840,16 @@
       </c>
       <c r="K56" s="6"/>
       <c r="L56" s="13" t="n">
-        <v>1.49E7</v>
+        <v>708294.0</v>
       </c>
       <c r="M56" s="13" t="n">
-        <v>1192000.0</v>
+        <v>56664.0</v>
       </c>
       <c r="N56" s="13" t="n">
-        <v>0.0</v>
+        <v>21906.0</v>
       </c>
       <c r="O56" s="13" t="n">
-        <v>1.6092E7</v>
+        <v>764958.0</v>
       </c>
       <c r="P56" s="6" t="inlineStr">
         <is>
@@ -3877,32 +3873,32 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>C26MTP</t>
+          <t>C26MRT</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>10101</t>
+          <t>19674</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>3501981599</t>
+          <t>3501013206</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI THỊNH PHÁT VN</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI BẠCH MAI</t>
         </is>
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t>Số 138 Nguyễn Thiện Thuật, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 01A Tô Nguyệt Đình, Phường Long Hương, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I57" s="7" t="inlineStr">
@@ -3912,21 +3908,21 @@
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
-          <t>Công ty TNHH Thạnh Hương Bến Đình</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K57" s="6"/>
       <c r="L57" s="13" t="n">
-        <v>4.0E7</v>
+        <v>3944445.0</v>
       </c>
       <c r="M57" s="13" t="n">
-        <v>4000000.0</v>
+        <v>315555.0</v>
       </c>
       <c r="N57" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O57" s="13" t="n">
-        <v>4.4E7</v>
+        <v>4260000.0</v>
       </c>
       <c r="P57" s="6" t="inlineStr">
         <is>
@@ -3950,32 +3946,32 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>C26MTK</t>
+          <t>C26MRT</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>3118</t>
+          <t>19874</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>3502242819</t>
+          <t>3501013206</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THOẠI KHANG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI BẠCH MAI</t>
         </is>
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>36 Trường Chinh, Khu phố Hải An, Xã Long Hải, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 01A Tô Nguyệt Đình, Phường Long Hương, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I58" s="7" t="inlineStr">
@@ -3990,14 +3986,16 @@
       </c>
       <c r="K58" s="6"/>
       <c r="L58" s="13" t="n">
-        <v>3.0345454E7</v>
+        <v>2425926.0</v>
       </c>
       <c r="M58" s="13" t="n">
-        <v>3034546.0</v>
-      </c>
-      <c r="N58" s="13"/>
+        <v>194074.0</v>
+      </c>
+      <c r="N58" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="O58" s="13" t="n">
-        <v>3.338E7</v>
+        <v>2620000.0</v>
       </c>
       <c r="P58" s="6" t="inlineStr">
         <is>
@@ -4021,32 +4019,32 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>C26MTK</t>
+          <t>C26MHD</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>3183</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>3502242819</t>
+          <t>3501663719</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THOẠI KHANG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HẢI ĐOÀN</t>
         </is>
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>36 Trường Chinh, Khu phố Hải An, Xã Long Hải, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 135 đường 2/9, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I59" s="7" t="inlineStr">
@@ -4061,14 +4059,16 @@
       </c>
       <c r="K59" s="6"/>
       <c r="L59" s="13" t="n">
-        <v>1.8657408E7</v>
+        <v>1.49E7</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>1492592.0</v>
-      </c>
-      <c r="N59" s="13"/>
+        <v>1192000.0</v>
+      </c>
+      <c r="N59" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="O59" s="13" t="n">
-        <v>2.015E7</v>
+        <v>1.6092E7</v>
       </c>
       <c r="P59" s="6" t="inlineStr">
         <is>
@@ -4092,32 +4092,32 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>C26MHT</t>
+          <t>C26MTP</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>6877</t>
+          <t>10101</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>3502324074</t>
+          <t>3501981599</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ HƯƠNG THỊNH PHÁT</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI THỊNH PHÁT VN</t>
         </is>
       </c>
       <c r="H60" s="6" t="inlineStr">
         <is>
-          <t>69 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 138 Nguyễn Thiện Thuật, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I60" s="7" t="inlineStr">
@@ -4127,21 +4127,21 @@
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>Công ty TNHH Thạnh Hương Bến Đình</t>
         </is>
       </c>
       <c r="K60" s="6"/>
       <c r="L60" s="13" t="n">
-        <v>1.90232E8</v>
+        <v>4.0E7</v>
       </c>
       <c r="M60" s="13" t="n">
-        <v>1.90232E7</v>
+        <v>4000000.0</v>
       </c>
       <c r="N60" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O60" s="13" t="n">
-        <v>2.092552E8</v>
+        <v>4.4E7</v>
       </c>
       <c r="P60" s="6" t="inlineStr">
         <is>
@@ -4165,32 +4165,32 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>C26MTD</t>
+          <t>C26MTK</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>6120</t>
+          <t>3118</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>3502344144</t>
+          <t>3502242819</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+          <t>CÔNG TY TNHH THOẠI KHANG</t>
         </is>
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+          <t>36 Trường Chinh, Khu phố Hải An, Xã Long Hải, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I61" s="7" t="inlineStr">
@@ -4205,16 +4205,14 @@
       </c>
       <c r="K61" s="6"/>
       <c r="L61" s="13" t="n">
-        <v>4.443182E7</v>
+        <v>3.0345454E7</v>
       </c>
       <c r="M61" s="13" t="n">
-        <v>4443180.0</v>
-      </c>
-      <c r="N61" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>3034546.0</v>
+      </c>
+      <c r="N61" s="13"/>
       <c r="O61" s="13" t="n">
-        <v>4.8875E7</v>
+        <v>3.338E7</v>
       </c>
       <c r="P61" s="6" t="inlineStr">
         <is>
@@ -4238,32 +4236,32 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>C26MTD</t>
+          <t>C26MTK</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>6128</t>
+          <t>3183</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>3502344144</t>
+          <t>3502242819</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+          <t>CÔNG TY TNHH THOẠI KHANG</t>
         </is>
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+          <t>36 Trường Chinh, Khu phố Hải An, Xã Long Hải, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I62" s="7" t="inlineStr">
@@ -4278,16 +4276,14 @@
       </c>
       <c r="K62" s="6"/>
       <c r="L62" s="13" t="n">
-        <v>2833333.0</v>
+        <v>1.8657408E7</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>226667.0</v>
-      </c>
-      <c r="N62" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>1492592.0</v>
+      </c>
+      <c r="N62" s="13"/>
       <c r="O62" s="13" t="n">
-        <v>3060000.0</v>
+        <v>2.015E7</v>
       </c>
       <c r="P62" s="6" t="inlineStr">
         <is>
@@ -4311,32 +4307,32 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>C26MTD</t>
+          <t>C26MHT</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>6156</t>
+          <t>6877</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>3502344144</t>
+          <t>3502324074</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ HƯƠNG THỊNH PHÁT</t>
         </is>
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+          <t>69 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I63" s="7" t="inlineStr">
@@ -4351,16 +4347,16 @@
       </c>
       <c r="K63" s="6"/>
       <c r="L63" s="13" t="n">
-        <v>2.7490909E7</v>
+        <v>1.90232E8</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>2749091.0</v>
+        <v>1.90232E7</v>
       </c>
       <c r="N63" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O63" s="13" t="n">
-        <v>3.024E7</v>
+        <v>2.092552E8</v>
       </c>
       <c r="P63" s="6" t="inlineStr">
         <is>
@@ -4384,32 +4380,32 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>C26MTD</t>
+          <t>C26MHT</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>6410</t>
+          <t>7059</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>3502344144</t>
+          <t>3502324074</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ HƯƠNG THỊNH PHÁT</t>
         </is>
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
-          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+          <t>69 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I64" s="7" t="inlineStr">
@@ -4424,16 +4420,16 @@
       </c>
       <c r="K64" s="6"/>
       <c r="L64" s="13" t="n">
-        <v>1.9818182E7</v>
+        <v>2.3779E8</v>
       </c>
       <c r="M64" s="13" t="n">
-        <v>1981818.0</v>
+        <v>2.3779E7</v>
       </c>
       <c r="N64" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O64" s="13" t="n">
-        <v>2.18E7</v>
+        <v>2.61569E8</v>
       </c>
       <c r="P64" s="6" t="inlineStr">
         <is>
@@ -4462,12 +4458,12 @@
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>6430</t>
+          <t>6120</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
@@ -4497,16 +4493,16 @@
       </c>
       <c r="K65" s="6"/>
       <c r="L65" s="13" t="n">
-        <v>6441499.0</v>
+        <v>4.443182E7</v>
       </c>
       <c r="M65" s="13" t="n">
-        <v>583501.0</v>
+        <v>4443180.0</v>
       </c>
       <c r="N65" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O65" s="13" t="n">
-        <v>7025000.0</v>
+        <v>4.8875E7</v>
       </c>
       <c r="P65" s="6" t="inlineStr">
         <is>
@@ -4535,12 +4531,12 @@
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>6526</t>
+          <t>6128</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="F66" s="7" t="inlineStr">
@@ -4570,16 +4566,16 @@
       </c>
       <c r="K66" s="6"/>
       <c r="L66" s="13" t="n">
-        <v>2.0363636E7</v>
+        <v>2833333.0</v>
       </c>
       <c r="M66" s="13" t="n">
-        <v>2036364.0</v>
+        <v>226667.0</v>
       </c>
       <c r="N66" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O66" s="13" t="n">
-        <v>2.24E7</v>
+        <v>3060000.0</v>
       </c>
       <c r="P66" s="6" t="inlineStr">
         <is>
@@ -4608,12 +4604,12 @@
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>6564</t>
+          <t>6156</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
@@ -4643,16 +4639,16 @@
       </c>
       <c r="K67" s="6"/>
       <c r="L67" s="13" t="n">
-        <v>1.4706398E7</v>
+        <v>2.7490909E7</v>
       </c>
       <c r="M67" s="13" t="n">
-        <v>1403602.0</v>
+        <v>2749091.0</v>
       </c>
       <c r="N67" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O67" s="13" t="n">
-        <v>1.611E7</v>
+        <v>3.024E7</v>
       </c>
       <c r="P67" s="6" t="inlineStr">
         <is>
@@ -4681,12 +4677,12 @@
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>6566</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr">
@@ -4716,16 +4712,16 @@
       </c>
       <c r="K68" s="6"/>
       <c r="L68" s="13" t="n">
-        <v>3789142.0</v>
+        <v>1.9818182E7</v>
       </c>
       <c r="M68" s="13" t="n">
-        <v>335858.0</v>
+        <v>1981818.0</v>
       </c>
       <c r="N68" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O68" s="13" t="n">
-        <v>4125000.0</v>
+        <v>2.18E7</v>
       </c>
       <c r="P68" s="6" t="inlineStr">
         <is>
@@ -4754,12 +4750,12 @@
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>6638</t>
+          <t>6430</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
@@ -4789,16 +4785,16 @@
       </c>
       <c r="K69" s="6"/>
       <c r="L69" s="13" t="n">
-        <v>3.7609091E7</v>
+        <v>6441499.0</v>
       </c>
       <c r="M69" s="13" t="n">
-        <v>3760909.0</v>
+        <v>583501.0</v>
       </c>
       <c r="N69" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O69" s="13" t="n">
-        <v>4.137E7</v>
+        <v>7025000.0</v>
       </c>
       <c r="P69" s="6" t="inlineStr">
         <is>
@@ -4827,12 +4823,12 @@
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>6644</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">
@@ -4862,16 +4858,16 @@
       </c>
       <c r="K70" s="6"/>
       <c r="L70" s="13" t="n">
-        <v>3.2181818E7</v>
+        <v>2.0363636E7</v>
       </c>
       <c r="M70" s="13" t="n">
-        <v>3218182.0</v>
+        <v>2036364.0</v>
       </c>
       <c r="N70" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O70" s="13" t="n">
-        <v>3.54E7</v>
+        <v>2.24E7</v>
       </c>
       <c r="P70" s="6" t="inlineStr">
         <is>
@@ -4900,12 +4896,12 @@
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>6790</t>
+          <t>6564</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
@@ -4935,16 +4931,16 @@
       </c>
       <c r="K71" s="6"/>
       <c r="L71" s="13" t="n">
-        <v>1.29545455E8</v>
+        <v>1.4706398E7</v>
       </c>
       <c r="M71" s="13" t="n">
-        <v>1.2954545E7</v>
+        <v>1403602.0</v>
       </c>
       <c r="N71" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O71" s="13" t="n">
-        <v>1.425E8</v>
+        <v>1.611E7</v>
       </c>
       <c r="P71" s="6" t="inlineStr">
         <is>
@@ -4968,32 +4964,32 @@
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>C26MTT</t>
+          <t>C26MTD</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>1389</t>
+          <t>6566</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>3502425499</t>
+          <t>3502344144</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH NPP TOÀN THẮNG PH</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
         </is>
       </c>
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>75/9/7 Phạm Hồng Thái, Phường Tam Thắng, Thành Phố Hồ Chí Minh</t>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I72" s="7" t="inlineStr">
@@ -5008,16 +5004,16 @@
       </c>
       <c r="K72" s="6"/>
       <c r="L72" s="13" t="n">
-        <v>4059260.0</v>
+        <v>3789142.0</v>
       </c>
       <c r="M72" s="13" t="n">
-        <v>324740.0</v>
+        <v>335858.0</v>
       </c>
       <c r="N72" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O72" s="13" t="n">
-        <v>4384000.0</v>
+        <v>4125000.0</v>
       </c>
       <c r="P72" s="6" t="inlineStr">
         <is>
@@ -5041,32 +5037,32 @@
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>C26MTA</t>
+          <t>C26MTD</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>6638</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>3502426622</t>
+          <t>3502344144</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẢO ANH VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
         </is>
       </c>
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>Tổ 12, ấp Phước Hưng, Xã Long Hải, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I73" s="7" t="inlineStr">
@@ -5081,16 +5077,16 @@
       </c>
       <c r="K73" s="6"/>
       <c r="L73" s="13" t="n">
-        <v>2.1348148E7</v>
+        <v>3.7609091E7</v>
       </c>
       <c r="M73" s="13" t="n">
-        <v>1707852.0</v>
+        <v>3760909.0</v>
       </c>
       <c r="N73" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O73" s="13" t="n">
-        <v>2.3056E7</v>
+        <v>4.137E7</v>
       </c>
       <c r="P73" s="6" t="inlineStr">
         <is>
@@ -5114,32 +5110,32 @@
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>C26MYY</t>
+          <t>C26MTD</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>10008</t>
+          <t>6644</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>3502474552</t>
+          <t>3502344144</t>
         </is>
       </c>
       <c r="G74" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI TRỌNG GIANG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
         </is>
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
-          <t>B16 Khu Tái Định Cư 199 Lô Khu Nhà Ở Đồi 2, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I74" s="7" t="inlineStr">
@@ -5154,16 +5150,16 @@
       </c>
       <c r="K74" s="6"/>
       <c r="L74" s="13" t="n">
-        <v>2727274.0</v>
+        <v>3.2181818E7</v>
       </c>
       <c r="M74" s="13" t="n">
-        <v>272727.0</v>
+        <v>3218182.0</v>
       </c>
       <c r="N74" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O74" s="13" t="n">
-        <v>3000001.0</v>
+        <v>3.54E7</v>
       </c>
       <c r="P74" s="6" t="inlineStr">
         <is>
@@ -5187,32 +5183,32 @@
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>C26MYY</t>
+          <t>C26MTD</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>9295</t>
+          <t>6790</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>3502474552</t>
+          <t>3502344144</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI TRỌNG GIANG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
         </is>
       </c>
       <c r="H75" s="6" t="inlineStr">
         <is>
-          <t>B16 Khu Tái Định Cư 199 Lô Khu Nhà Ở Đồi 2, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I75" s="7" t="inlineStr">
@@ -5227,16 +5223,16 @@
       </c>
       <c r="K75" s="6"/>
       <c r="L75" s="13" t="n">
-        <v>2727274.0</v>
+        <v>1.29545455E8</v>
       </c>
       <c r="M75" s="13" t="n">
-        <v>272727.0</v>
+        <v>1.2954545E7</v>
       </c>
       <c r="N75" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O75" s="13" t="n">
-        <v>3000001.0</v>
+        <v>1.425E8</v>
       </c>
       <c r="P75" s="6" t="inlineStr">
         <is>
@@ -5260,32 +5256,32 @@
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>C26MYY</t>
+          <t>C26MTD</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>9324</t>
+          <t>6845</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr">
         <is>
-          <t>3502474552</t>
+          <t>3502344144</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI TRỌNG GIANG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
         </is>
       </c>
       <c r="H76" s="6" t="inlineStr">
         <is>
-          <t>B16 Khu Tái Định Cư 199 Lô Khu Nhà Ở Đồi 2, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I76" s="7" t="inlineStr">
@@ -5300,16 +5296,16 @@
       </c>
       <c r="K76" s="6"/>
       <c r="L76" s="13" t="n">
-        <v>2727274.0</v>
+        <v>1.8690909E7</v>
       </c>
       <c r="M76" s="13" t="n">
-        <v>272727.0</v>
+        <v>1869091.0</v>
       </c>
       <c r="N76" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O76" s="13" t="n">
-        <v>3000001.0</v>
+        <v>2.056E7</v>
       </c>
       <c r="P76" s="6" t="inlineStr">
         <is>
@@ -5333,32 +5329,32 @@
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>C26MYY</t>
+          <t>C26MTT</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>9523</t>
+          <t>1389</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>3502474552</t>
+          <t>3502425499</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI TRỌNG GIANG</t>
+          <t>CÔNG TY TNHH NPP TOÀN THẮNG PH</t>
         </is>
       </c>
       <c r="H77" s="6" t="inlineStr">
         <is>
-          <t>B16 Khu Tái Định Cư 199 Lô Khu Nhà Ở Đồi 2, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>75/9/7 Phạm Hồng Thái, Phường Tam Thắng, Thành Phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I77" s="7" t="inlineStr">
@@ -5373,16 +5369,16 @@
       </c>
       <c r="K77" s="6"/>
       <c r="L77" s="13" t="n">
-        <v>2727274.0</v>
+        <v>4059260.0</v>
       </c>
       <c r="M77" s="13" t="n">
-        <v>272727.0</v>
+        <v>324740.0</v>
       </c>
       <c r="N77" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O77" s="13" t="n">
-        <v>3000001.0</v>
+        <v>4384000.0</v>
       </c>
       <c r="P77" s="6" t="inlineStr">
         <is>
@@ -5406,32 +5402,32 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>C26MYY</t>
+          <t>C26MTA</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>3870</t>
+          <t>395</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>3502483525</t>
+          <t>3502426622</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI ĐẠI Ý 79</t>
+          <t>CÔNG TY TNHH THẢO ANH VŨNG TÀU</t>
         </is>
       </c>
       <c r="H78" s="6" t="inlineStr">
         <is>
-          <t>Số 22/18/29 đường Nam Kỳ Khởi Nghĩa, Phường Vũng Tàu, TP Hồ Chí Minh , Việt Nam</t>
+          <t>Tổ 12, ấp Phước Hưng, Xã Long Hải, TP Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I78" s="7" t="inlineStr">
@@ -5441,21 +5437,21 @@
       </c>
       <c r="J78" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K78" s="6"/>
       <c r="L78" s="13" t="n">
-        <v>7.8272727E7</v>
+        <v>2.1348148E7</v>
       </c>
       <c r="M78" s="13" t="n">
-        <v>7827273.0</v>
+        <v>1707852.0</v>
       </c>
       <c r="N78" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O78" s="13" t="n">
-        <v>8.61E7</v>
+        <v>2.3056E7</v>
       </c>
       <c r="P78" s="6" t="inlineStr">
         <is>
@@ -5479,32 +5475,32 @@
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>C26MNL</t>
+          <t>C26MYY</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>2509</t>
+          <t>10008</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>3502547930</t>
+          <t>3502474552</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI TRỌNG GIANG</t>
         </is>
       </c>
       <c r="H79" s="6" t="inlineStr">
         <is>
-          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>B16 Khu Tái Định Cư 199 Lô Khu Nhà Ở Đồi 2, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I79" s="7" t="inlineStr">
@@ -5519,16 +5515,16 @@
       </c>
       <c r="K79" s="6"/>
       <c r="L79" s="13" t="n">
-        <v>4.2592593E7</v>
+        <v>2727274.0</v>
       </c>
       <c r="M79" s="13" t="n">
-        <v>3407407.0</v>
+        <v>272727.0</v>
       </c>
       <c r="N79" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O79" s="13" t="n">
-        <v>4.6E7</v>
+        <v>3000001.0</v>
       </c>
       <c r="P79" s="6" t="inlineStr">
         <is>
@@ -5552,32 +5548,32 @@
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>C26MNL</t>
+          <t>C26MYY</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>2515</t>
+          <t>9295</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>3502547930</t>
+          <t>3502474552</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI TRỌNG GIANG</t>
         </is>
       </c>
       <c r="H80" s="6" t="inlineStr">
         <is>
-          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>B16 Khu Tái Định Cư 199 Lô Khu Nhà Ở Đồi 2, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I80" s="7" t="inlineStr">
@@ -5592,16 +5588,16 @@
       </c>
       <c r="K80" s="6"/>
       <c r="L80" s="13" t="n">
-        <v>1.5185185E7</v>
+        <v>2727274.0</v>
       </c>
       <c r="M80" s="13" t="n">
-        <v>1214815.0</v>
+        <v>272727.0</v>
       </c>
       <c r="N80" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O80" s="13" t="n">
-        <v>1.64E7</v>
+        <v>3000001.0</v>
       </c>
       <c r="P80" s="6" t="inlineStr">
         <is>
@@ -5625,32 +5621,32 @@
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>C26MNL</t>
+          <t>C26MYY</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>2549</t>
+          <t>9324</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>3502547930</t>
+          <t>3502474552</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI TRỌNG GIANG</t>
         </is>
       </c>
       <c r="H81" s="6" t="inlineStr">
         <is>
-          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>B16 Khu Tái Định Cư 199 Lô Khu Nhà Ở Đồi 2, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I81" s="7" t="inlineStr">
@@ -5665,16 +5661,16 @@
       </c>
       <c r="K81" s="6"/>
       <c r="L81" s="13" t="n">
-        <v>3320000.0</v>
+        <v>2727274.0</v>
       </c>
       <c r="M81" s="13" t="n">
-        <v>265600.0</v>
+        <v>272727.0</v>
       </c>
       <c r="N81" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O81" s="13" t="n">
-        <v>3585600.0</v>
+        <v>3000001.0</v>
       </c>
       <c r="P81" s="6" t="inlineStr">
         <is>
@@ -5698,32 +5694,32 @@
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>C26MNL</t>
+          <t>C26MYY</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>2643</t>
+          <t>9523</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="F82" s="7" t="inlineStr">
         <is>
-          <t>3502547930</t>
+          <t>3502474552</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI TRỌNG GIANG</t>
         </is>
       </c>
       <c r="H82" s="6" t="inlineStr">
         <is>
-          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>B16 Khu Tái Định Cư 199 Lô Khu Nhà Ở Đồi 2, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I82" s="7" t="inlineStr">
@@ -5738,16 +5734,16 @@
       </c>
       <c r="K82" s="6"/>
       <c r="L82" s="13" t="n">
-        <v>2.5833333E7</v>
+        <v>2727274.0</v>
       </c>
       <c r="M82" s="13" t="n">
-        <v>2066667.0</v>
+        <v>272727.0</v>
       </c>
       <c r="N82" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O82" s="13" t="n">
-        <v>2.79E7</v>
+        <v>3000001.0</v>
       </c>
       <c r="P82" s="6" t="inlineStr">
         <is>
@@ -5771,32 +5767,32 @@
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>C26MNL</t>
+          <t>C26MYY</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>2715</t>
+          <t>3870</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>3502547930</t>
+          <t>3502483525</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI ĐẠI Ý 79</t>
         </is>
       </c>
       <c r="H83" s="6" t="inlineStr">
         <is>
-          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 22/18/29 đường Nam Kỳ Khởi Nghĩa, Phường Vũng Tàu, TP Hồ Chí Minh , Việt Nam</t>
         </is>
       </c>
       <c r="I83" s="7" t="inlineStr">
@@ -5806,21 +5802,21 @@
       </c>
       <c r="J83" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K83" s="6"/>
       <c r="L83" s="13" t="n">
-        <v>9987037.0</v>
+        <v>7.8272727E7</v>
       </c>
       <c r="M83" s="13" t="n">
-        <v>798963.0</v>
+        <v>7827273.0</v>
       </c>
       <c r="N83" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O83" s="13" t="n">
-        <v>1.0786E7</v>
+        <v>8.61E7</v>
       </c>
       <c r="P83" s="6" t="inlineStr">
         <is>
@@ -5849,12 +5845,12 @@
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>2509</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="F84" s="7" t="inlineStr">
@@ -5884,16 +5880,16 @@
       </c>
       <c r="K84" s="6"/>
       <c r="L84" s="13" t="n">
-        <v>1425926.0</v>
+        <v>4.2592593E7</v>
       </c>
       <c r="M84" s="13" t="n">
-        <v>114074.0</v>
+        <v>3407407.0</v>
       </c>
       <c r="N84" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O84" s="13" t="n">
-        <v>1540000.0</v>
+        <v>4.6E7</v>
       </c>
       <c r="P84" s="6" t="inlineStr">
         <is>
@@ -5922,12 +5918,12 @@
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>2772</t>
+          <t>2515</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="F85" s="7" t="inlineStr">
@@ -5957,16 +5953,16 @@
       </c>
       <c r="K85" s="6"/>
       <c r="L85" s="13" t="n">
-        <v>3796296.0</v>
+        <v>1.5185185E7</v>
       </c>
       <c r="M85" s="13" t="n">
-        <v>303704.0</v>
+        <v>1214815.0</v>
       </c>
       <c r="N85" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O85" s="13" t="n">
-        <v>4100000.0</v>
+        <v>1.64E7</v>
       </c>
       <c r="P85" s="6" t="inlineStr">
         <is>
@@ -5995,12 +5991,12 @@
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>2813</t>
+          <t>2549</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="F86" s="7" t="inlineStr">
@@ -6030,16 +6026,16 @@
       </c>
       <c r="K86" s="6"/>
       <c r="L86" s="13" t="n">
-        <v>2138889.0</v>
+        <v>3320000.0</v>
       </c>
       <c r="M86" s="13" t="n">
-        <v>171111.0</v>
+        <v>265600.0</v>
       </c>
       <c r="N86" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O86" s="13" t="n">
-        <v>2310000.0</v>
+        <v>3585600.0</v>
       </c>
       <c r="P86" s="6" t="inlineStr">
         <is>
@@ -6058,64 +6054,502 @@
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>C26MNL</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>2643</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
+          <t>3502547930</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+        </is>
+      </c>
+      <c r="H87" s="6" t="inlineStr">
+        <is>
+          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I87" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J87" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K87" s="6"/>
+      <c r="L87" s="13" t="n">
+        <v>2.5833333E7</v>
+      </c>
+      <c r="M87" s="13" t="n">
+        <v>2066667.0</v>
+      </c>
+      <c r="N87" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O87" s="13" t="n">
+        <v>2.79E7</v>
+      </c>
+      <c r="P87" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q87" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="n">
+        <v>82.0</v>
+      </c>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>C26MNL</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>2715</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="F88" s="7" t="inlineStr">
+        <is>
+          <t>3502547930</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+        </is>
+      </c>
+      <c r="H88" s="6" t="inlineStr">
+        <is>
+          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I88" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J88" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K88" s="6"/>
+      <c r="L88" s="13" t="n">
+        <v>9987037.0</v>
+      </c>
+      <c r="M88" s="13" t="n">
+        <v>798963.0</v>
+      </c>
+      <c r="N88" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O88" s="13" t="n">
+        <v>1.0786E7</v>
+      </c>
+      <c r="P88" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q88" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="n">
+        <v>83.0</v>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>C26MNL</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>2753</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t>3502547930</t>
+        </is>
+      </c>
+      <c r="G89" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+        </is>
+      </c>
+      <c r="H89" s="6" t="inlineStr">
+        <is>
+          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I89" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J89" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K89" s="6"/>
+      <c r="L89" s="13" t="n">
+        <v>1425926.0</v>
+      </c>
+      <c r="M89" s="13" t="n">
+        <v>114074.0</v>
+      </c>
+      <c r="N89" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O89" s="13" t="n">
+        <v>1540000.0</v>
+      </c>
+      <c r="P89" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q89" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="n">
+        <v>84.0</v>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>C26MNL</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>2772</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
+          <t>3502547930</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+        </is>
+      </c>
+      <c r="H90" s="6" t="inlineStr">
+        <is>
+          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I90" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J90" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K90" s="6"/>
+      <c r="L90" s="13" t="n">
+        <v>3796296.0</v>
+      </c>
+      <c r="M90" s="13" t="n">
+        <v>303704.0</v>
+      </c>
+      <c r="N90" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O90" s="13" t="n">
+        <v>4100000.0</v>
+      </c>
+      <c r="P90" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q90" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="n">
+        <v>85.0</v>
+      </c>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>C26MNL</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>2813</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>19/09/2026</t>
+        </is>
+      </c>
+      <c r="F91" s="7" t="inlineStr">
+        <is>
+          <t>3502547930</t>
+        </is>
+      </c>
+      <c r="G91" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+        </is>
+      </c>
+      <c r="H91" s="6" t="inlineStr">
+        <is>
+          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I91" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J91" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K91" s="6"/>
+      <c r="L91" s="13" t="n">
+        <v>2138889.0</v>
+      </c>
+      <c r="M91" s="13" t="n">
+        <v>171111.0</v>
+      </c>
+      <c r="N91" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O91" s="13" t="n">
+        <v>2310000.0</v>
+      </c>
+      <c r="P91" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q91" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="n">
+        <v>86.0</v>
+      </c>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>C26MNL</t>
+        </is>
+      </c>
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>2909</t>
+        </is>
+      </c>
+      <c r="E92" s="7" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="F92" s="7" t="inlineStr">
+        <is>
+          <t>3502547930</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+        </is>
+      </c>
+      <c r="H92" s="6" t="inlineStr">
+        <is>
+          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I92" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J92" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K92" s="6"/>
+      <c r="L92" s="13" t="n">
+        <v>2.8564815E7</v>
+      </c>
+      <c r="M92" s="13" t="n">
+        <v>2285185.0</v>
+      </c>
+      <c r="N92" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O92" s="13" t="n">
+        <v>3.085E7</v>
+      </c>
+      <c r="P92" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q92" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="n">
+        <v>87.0</v>
+      </c>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C87" s="6" t="inlineStr">
+      <c r="C93" s="6" t="inlineStr">
         <is>
           <t>C26MYX</t>
         </is>
       </c>
-      <c r="D87" s="7" t="inlineStr">
+      <c r="D93" s="7" t="inlineStr">
         <is>
           <t>11088</t>
         </is>
       </c>
-      <c r="E87" s="7" t="inlineStr">
+      <c r="E93" s="7" t="inlineStr">
         <is>
           <t>09/09/2026</t>
         </is>
       </c>
-      <c r="F87" s="7" t="inlineStr">
+      <c r="F93" s="7" t="inlineStr">
         <is>
           <t>3502573440</t>
         </is>
       </c>
-      <c r="G87" s="6" t="inlineStr">
+      <c r="G93" s="6" t="inlineStr">
         <is>
           <t>Trạm Y tế phường Tam Thắng</t>
         </is>
       </c>
-      <c r="H87" s="6" t="inlineStr">
+      <c r="H93" s="6" t="inlineStr">
         <is>
           <t>số 278 Lê Lợi, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
-      <c r="I87" s="7" t="inlineStr">
-        <is>
-          <t>3502550210</t>
-        </is>
-      </c>
-      <c r="J87" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
-        </is>
-      </c>
-      <c r="K87" s="6"/>
-      <c r="L87" s="13"/>
-      <c r="M87" s="13"/>
-      <c r="N87" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O87" s="13" t="n">
+      <c r="I93" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J93" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K93" s="6"/>
+      <c r="L93" s="13"/>
+      <c r="M93" s="13"/>
+      <c r="N93" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O93" s="13" t="n">
         <v>2411000.0</v>
       </c>
-      <c r="P87" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q87" s="6" t="inlineStr">
+      <c r="P93" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q93" s="6" t="inlineStr">
         <is>
           <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
         </is>

--- a/Hoadon/HD2026/HDVao/9/3502550210_HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HD2026/HDVao/9/3502550210_HDDienTuMayTinhTien.xlsx
@@ -4453,32 +4453,32 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>C26MTD</t>
+          <t>C26MHT</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>6120</t>
+          <t>7082</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>3502344144</t>
+          <t>3502324074</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ HƯƠNG THỊNH PHÁT</t>
         </is>
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+          <t>69 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I65" s="7" t="inlineStr">
@@ -4493,16 +4493,16 @@
       </c>
       <c r="K65" s="6"/>
       <c r="L65" s="13" t="n">
-        <v>4.443182E7</v>
+        <v>2.85348E8</v>
       </c>
       <c r="M65" s="13" t="n">
-        <v>4443180.0</v>
+        <v>2.85348E7</v>
       </c>
       <c r="N65" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O65" s="13" t="n">
-        <v>4.8875E7</v>
+        <v>3.138828E8</v>
       </c>
       <c r="P65" s="6" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>6128</t>
+          <t>6120</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
@@ -4566,16 +4566,16 @@
       </c>
       <c r="K66" s="6"/>
       <c r="L66" s="13" t="n">
-        <v>2833333.0</v>
+        <v>4.443182E7</v>
       </c>
       <c r="M66" s="13" t="n">
-        <v>226667.0</v>
+        <v>4443180.0</v>
       </c>
       <c r="N66" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O66" s="13" t="n">
-        <v>3060000.0</v>
+        <v>4.8875E7</v>
       </c>
       <c r="P66" s="6" t="inlineStr">
         <is>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>6156</t>
+          <t>6128</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
@@ -4639,16 +4639,16 @@
       </c>
       <c r="K67" s="6"/>
       <c r="L67" s="13" t="n">
-        <v>2.7490909E7</v>
+        <v>2833333.0</v>
       </c>
       <c r="M67" s="13" t="n">
-        <v>2749091.0</v>
+        <v>226667.0</v>
       </c>
       <c r="N67" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O67" s="13" t="n">
-        <v>3.024E7</v>
+        <v>3060000.0</v>
       </c>
       <c r="P67" s="6" t="inlineStr">
         <is>
@@ -4677,12 +4677,12 @@
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>6410</t>
+          <t>6156</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr">
@@ -4712,16 +4712,16 @@
       </c>
       <c r="K68" s="6"/>
       <c r="L68" s="13" t="n">
-        <v>1.9818182E7</v>
+        <v>2.7490909E7</v>
       </c>
       <c r="M68" s="13" t="n">
-        <v>1981818.0</v>
+        <v>2749091.0</v>
       </c>
       <c r="N68" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O68" s="13" t="n">
-        <v>2.18E7</v>
+        <v>3.024E7</v>
       </c>
       <c r="P68" s="6" t="inlineStr">
         <is>
@@ -4750,12 +4750,12 @@
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>6430</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
@@ -4785,16 +4785,16 @@
       </c>
       <c r="K69" s="6"/>
       <c r="L69" s="13" t="n">
-        <v>6441499.0</v>
+        <v>1.9818182E7</v>
       </c>
       <c r="M69" s="13" t="n">
-        <v>583501.0</v>
+        <v>1981818.0</v>
       </c>
       <c r="N69" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O69" s="13" t="n">
-        <v>7025000.0</v>
+        <v>2.18E7</v>
       </c>
       <c r="P69" s="6" t="inlineStr">
         <is>
@@ -4823,12 +4823,12 @@
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>6526</t>
+          <t>6430</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">
@@ -4858,16 +4858,16 @@
       </c>
       <c r="K70" s="6"/>
       <c r="L70" s="13" t="n">
-        <v>2.0363636E7</v>
+        <v>6441499.0</v>
       </c>
       <c r="M70" s="13" t="n">
-        <v>2036364.0</v>
+        <v>583501.0</v>
       </c>
       <c r="N70" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O70" s="13" t="n">
-        <v>2.24E7</v>
+        <v>7025000.0</v>
       </c>
       <c r="P70" s="6" t="inlineStr">
         <is>
@@ -4896,12 +4896,12 @@
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>6564</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
@@ -4931,16 +4931,16 @@
       </c>
       <c r="K71" s="6"/>
       <c r="L71" s="13" t="n">
-        <v>1.4706398E7</v>
+        <v>2.0363636E7</v>
       </c>
       <c r="M71" s="13" t="n">
-        <v>1403602.0</v>
+        <v>2036364.0</v>
       </c>
       <c r="N71" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O71" s="13" t="n">
-        <v>1.611E7</v>
+        <v>2.24E7</v>
       </c>
       <c r="P71" s="6" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>6566</t>
+          <t>6564</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
@@ -5004,16 +5004,16 @@
       </c>
       <c r="K72" s="6"/>
       <c r="L72" s="13" t="n">
-        <v>3789142.0</v>
+        <v>1.4706398E7</v>
       </c>
       <c r="M72" s="13" t="n">
-        <v>335858.0</v>
+        <v>1403602.0</v>
       </c>
       <c r="N72" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O72" s="13" t="n">
-        <v>4125000.0</v>
+        <v>1.611E7</v>
       </c>
       <c r="P72" s="6" t="inlineStr">
         <is>
@@ -5042,12 +5042,12 @@
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>6638</t>
+          <t>6566</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr">
@@ -5077,16 +5077,16 @@
       </c>
       <c r="K73" s="6"/>
       <c r="L73" s="13" t="n">
-        <v>3.7609091E7</v>
+        <v>3789142.0</v>
       </c>
       <c r="M73" s="13" t="n">
-        <v>3760909.0</v>
+        <v>335858.0</v>
       </c>
       <c r="N73" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O73" s="13" t="n">
-        <v>4.137E7</v>
+        <v>4125000.0</v>
       </c>
       <c r="P73" s="6" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>6644</t>
+          <t>6638</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
@@ -5150,16 +5150,16 @@
       </c>
       <c r="K74" s="6"/>
       <c r="L74" s="13" t="n">
-        <v>3.2181818E7</v>
+        <v>3.7609091E7</v>
       </c>
       <c r="M74" s="13" t="n">
-        <v>3218182.0</v>
+        <v>3760909.0</v>
       </c>
       <c r="N74" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O74" s="13" t="n">
-        <v>3.54E7</v>
+        <v>4.137E7</v>
       </c>
       <c r="P74" s="6" t="inlineStr">
         <is>
@@ -5188,12 +5188,12 @@
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>6790</t>
+          <t>6644</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="F75" s="7" t="inlineStr">
@@ -5223,16 +5223,16 @@
       </c>
       <c r="K75" s="6"/>
       <c r="L75" s="13" t="n">
-        <v>1.29545455E8</v>
+        <v>3.2181818E7</v>
       </c>
       <c r="M75" s="13" t="n">
-        <v>1.2954545E7</v>
+        <v>3218182.0</v>
       </c>
       <c r="N75" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O75" s="13" t="n">
-        <v>1.425E8</v>
+        <v>3.54E7</v>
       </c>
       <c r="P75" s="6" t="inlineStr">
         <is>
@@ -5261,12 +5261,12 @@
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>6845</t>
+          <t>6790</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr">
@@ -5296,16 +5296,16 @@
       </c>
       <c r="K76" s="6"/>
       <c r="L76" s="13" t="n">
-        <v>1.8690909E7</v>
+        <v>1.29545455E8</v>
       </c>
       <c r="M76" s="13" t="n">
-        <v>1869091.0</v>
+        <v>1.2954545E7</v>
       </c>
       <c r="N76" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O76" s="13" t="n">
-        <v>2.056E7</v>
+        <v>1.425E8</v>
       </c>
       <c r="P76" s="6" t="inlineStr">
         <is>
@@ -5329,32 +5329,32 @@
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>C26MTT</t>
+          <t>C26MTD</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>1389</t>
+          <t>6845</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>3502425499</t>
+          <t>3502344144</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH NPP TOÀN THẮNG PH</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
         </is>
       </c>
       <c r="H77" s="6" t="inlineStr">
         <is>
-          <t>75/9/7 Phạm Hồng Thái, Phường Tam Thắng, Thành Phố Hồ Chí Minh</t>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I77" s="7" t="inlineStr">
@@ -5369,16 +5369,16 @@
       </c>
       <c r="K77" s="6"/>
       <c r="L77" s="13" t="n">
-        <v>4059260.0</v>
+        <v>1.8690909E7</v>
       </c>
       <c r="M77" s="13" t="n">
-        <v>324740.0</v>
+        <v>1869091.0</v>
       </c>
       <c r="N77" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O77" s="13" t="n">
-        <v>4384000.0</v>
+        <v>2.056E7</v>
       </c>
       <c r="P77" s="6" t="inlineStr">
         <is>
@@ -5402,32 +5402,32 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>C26MTA</t>
+          <t>C26MTT</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>1389</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>3502426622</t>
+          <t>3502425499</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẢO ANH VŨNG TÀU</t>
+          <t>CÔNG TY TNHH NPP TOÀN THẮNG PH</t>
         </is>
       </c>
       <c r="H78" s="6" t="inlineStr">
         <is>
-          <t>Tổ 12, ấp Phước Hưng, Xã Long Hải, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>75/9/7 Phạm Hồng Thái, Phường Tam Thắng, Thành Phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I78" s="7" t="inlineStr">
@@ -5442,16 +5442,16 @@
       </c>
       <c r="K78" s="6"/>
       <c r="L78" s="13" t="n">
-        <v>2.1348148E7</v>
+        <v>4059260.0</v>
       </c>
       <c r="M78" s="13" t="n">
-        <v>1707852.0</v>
+        <v>324740.0</v>
       </c>
       <c r="N78" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O78" s="13" t="n">
-        <v>2.3056E7</v>
+        <v>4384000.0</v>
       </c>
       <c r="P78" s="6" t="inlineStr">
         <is>
@@ -5475,32 +5475,32 @@
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>C26MYY</t>
+          <t>C26MTA</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>10008</t>
+          <t>395</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>3502474552</t>
+          <t>3502426622</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI TRỌNG GIANG</t>
+          <t>CÔNG TY TNHH THẢO ANH VŨNG TÀU</t>
         </is>
       </c>
       <c r="H79" s="6" t="inlineStr">
         <is>
-          <t>B16 Khu Tái Định Cư 199 Lô Khu Nhà Ở Đồi 2, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>Tổ 12, ấp Phước Hưng, Xã Long Hải, TP Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I79" s="7" t="inlineStr">
@@ -5515,16 +5515,16 @@
       </c>
       <c r="K79" s="6"/>
       <c r="L79" s="13" t="n">
-        <v>2727274.0</v>
+        <v>2.1348148E7</v>
       </c>
       <c r="M79" s="13" t="n">
-        <v>272727.0</v>
+        <v>1707852.0</v>
       </c>
       <c r="N79" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O79" s="13" t="n">
-        <v>3000001.0</v>
+        <v>2.3056E7</v>
       </c>
       <c r="P79" s="6" t="inlineStr">
         <is>
@@ -5553,12 +5553,12 @@
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>9295</t>
+          <t>10008</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="F80" s="7" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>9324</t>
+          <t>9295</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="F81" s="7" t="inlineStr">
@@ -5699,12 +5699,12 @@
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>9523</t>
+          <t>9324</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="F82" s="7" t="inlineStr">
@@ -5772,27 +5772,27 @@
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>3870</t>
+          <t>9523</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>3502483525</t>
+          <t>3502474552</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI ĐẠI Ý 79</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI TRỌNG GIANG</t>
         </is>
       </c>
       <c r="H83" s="6" t="inlineStr">
         <is>
-          <t>Số 22/18/29 đường Nam Kỳ Khởi Nghĩa, Phường Vũng Tàu, TP Hồ Chí Minh , Việt Nam</t>
+          <t>B16 Khu Tái Định Cư 199 Lô Khu Nhà Ở Đồi 2, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I83" s="7" t="inlineStr">
@@ -5802,21 +5802,21 @@
       </c>
       <c r="J83" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K83" s="6"/>
       <c r="L83" s="13" t="n">
-        <v>7.8272727E7</v>
+        <v>2727274.0</v>
       </c>
       <c r="M83" s="13" t="n">
-        <v>7827273.0</v>
+        <v>272727.0</v>
       </c>
       <c r="N83" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O83" s="13" t="n">
-        <v>8.61E7</v>
+        <v>3000001.0</v>
       </c>
       <c r="P83" s="6" t="inlineStr">
         <is>
@@ -5840,32 +5840,32 @@
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>C26MNL</t>
+          <t>C26MYY</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>2509</t>
+          <t>3870</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="F84" s="7" t="inlineStr">
         <is>
-          <t>3502547930</t>
+          <t>3502483525</t>
         </is>
       </c>
       <c r="G84" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI ĐẠI Ý 79</t>
         </is>
       </c>
       <c r="H84" s="6" t="inlineStr">
         <is>
-          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 22/18/29 đường Nam Kỳ Khởi Nghĩa, Phường Vũng Tàu, TP Hồ Chí Minh , Việt Nam</t>
         </is>
       </c>
       <c r="I84" s="7" t="inlineStr">
@@ -5875,21 +5875,21 @@
       </c>
       <c r="J84" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K84" s="6"/>
       <c r="L84" s="13" t="n">
-        <v>4.2592593E7</v>
+        <v>7.8272727E7</v>
       </c>
       <c r="M84" s="13" t="n">
-        <v>3407407.0</v>
+        <v>7827273.0</v>
       </c>
       <c r="N84" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O84" s="13" t="n">
-        <v>4.6E7</v>
+        <v>8.61E7</v>
       </c>
       <c r="P84" s="6" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>2515</t>
+          <t>2509</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
@@ -5953,16 +5953,16 @@
       </c>
       <c r="K85" s="6"/>
       <c r="L85" s="13" t="n">
-        <v>1.5185185E7</v>
+        <v>4.2592593E7</v>
       </c>
       <c r="M85" s="13" t="n">
-        <v>1214815.0</v>
+        <v>3407407.0</v>
       </c>
       <c r="N85" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O85" s="13" t="n">
-        <v>1.64E7</v>
+        <v>4.6E7</v>
       </c>
       <c r="P85" s="6" t="inlineStr">
         <is>
@@ -5991,12 +5991,12 @@
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>2549</t>
+          <t>2515</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="F86" s="7" t="inlineStr">
@@ -6026,16 +6026,16 @@
       </c>
       <c r="K86" s="6"/>
       <c r="L86" s="13" t="n">
-        <v>3320000.0</v>
+        <v>1.5185185E7</v>
       </c>
       <c r="M86" s="13" t="n">
-        <v>265600.0</v>
+        <v>1214815.0</v>
       </c>
       <c r="N86" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O86" s="13" t="n">
-        <v>3585600.0</v>
+        <v>1.64E7</v>
       </c>
       <c r="P86" s="6" t="inlineStr">
         <is>
@@ -6064,12 +6064,12 @@
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>2643</t>
+          <t>2549</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr">
@@ -6099,16 +6099,16 @@
       </c>
       <c r="K87" s="6"/>
       <c r="L87" s="13" t="n">
-        <v>2.5833333E7</v>
+        <v>3320000.0</v>
       </c>
       <c r="M87" s="13" t="n">
-        <v>2066667.0</v>
+        <v>265600.0</v>
       </c>
       <c r="N87" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O87" s="13" t="n">
-        <v>2.79E7</v>
+        <v>3585600.0</v>
       </c>
       <c r="P87" s="6" t="inlineStr">
         <is>
@@ -6137,12 +6137,12 @@
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>2715</t>
+          <t>2643</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="F88" s="7" t="inlineStr">
@@ -6172,16 +6172,16 @@
       </c>
       <c r="K88" s="6"/>
       <c r="L88" s="13" t="n">
-        <v>9987037.0</v>
+        <v>2.5833333E7</v>
       </c>
       <c r="M88" s="13" t="n">
-        <v>798963.0</v>
+        <v>2066667.0</v>
       </c>
       <c r="N88" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O88" s="13" t="n">
-        <v>1.0786E7</v>
+        <v>2.79E7</v>
       </c>
       <c r="P88" s="6" t="inlineStr">
         <is>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>2715</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="F89" s="7" t="inlineStr">
@@ -6245,16 +6245,16 @@
       </c>
       <c r="K89" s="6"/>
       <c r="L89" s="13" t="n">
-        <v>1425926.0</v>
+        <v>9987037.0</v>
       </c>
       <c r="M89" s="13" t="n">
-        <v>114074.0</v>
+        <v>798963.0</v>
       </c>
       <c r="N89" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O89" s="13" t="n">
-        <v>1540000.0</v>
+        <v>1.0786E7</v>
       </c>
       <c r="P89" s="6" t="inlineStr">
         <is>
@@ -6283,12 +6283,12 @@
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>2772</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="F90" s="7" t="inlineStr">
@@ -6318,16 +6318,16 @@
       </c>
       <c r="K90" s="6"/>
       <c r="L90" s="13" t="n">
-        <v>3796296.0</v>
+        <v>1425926.0</v>
       </c>
       <c r="M90" s="13" t="n">
-        <v>303704.0</v>
+        <v>114074.0</v>
       </c>
       <c r="N90" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O90" s="13" t="n">
-        <v>4100000.0</v>
+        <v>1540000.0</v>
       </c>
       <c r="P90" s="6" t="inlineStr">
         <is>
@@ -6356,12 +6356,12 @@
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>2813</t>
+          <t>2772</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr">
@@ -6391,16 +6391,16 @@
       </c>
       <c r="K91" s="6"/>
       <c r="L91" s="13" t="n">
-        <v>2138889.0</v>
+        <v>3796296.0</v>
       </c>
       <c r="M91" s="13" t="n">
-        <v>171111.0</v>
+        <v>303704.0</v>
       </c>
       <c r="N91" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O91" s="13" t="n">
-        <v>2310000.0</v>
+        <v>4100000.0</v>
       </c>
       <c r="P91" s="6" t="inlineStr">
         <is>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>2909</t>
+          <t>2813</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr">
@@ -6464,16 +6464,16 @@
       </c>
       <c r="K92" s="6"/>
       <c r="L92" s="13" t="n">
-        <v>2.8564815E7</v>
+        <v>2138889.0</v>
       </c>
       <c r="M92" s="13" t="n">
-        <v>2285185.0</v>
+        <v>171111.0</v>
       </c>
       <c r="N92" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O92" s="13" t="n">
-        <v>3.085E7</v>
+        <v>2310000.0</v>
       </c>
       <c r="P92" s="6" t="inlineStr">
         <is>
@@ -6492,64 +6492,137 @@
       </c>
       <c r="B93" s="7" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>C26MNL</t>
+        </is>
+      </c>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>2909</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="F93" s="7" t="inlineStr">
+        <is>
+          <t>3502547930</t>
+        </is>
+      </c>
+      <c r="G93" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+        </is>
+      </c>
+      <c r="H93" s="6" t="inlineStr">
+        <is>
+          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I93" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J93" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K93" s="6"/>
+      <c r="L93" s="13" t="n">
+        <v>2.8564815E7</v>
+      </c>
+      <c r="M93" s="13" t="n">
+        <v>2285185.0</v>
+      </c>
+      <c r="N93" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O93" s="13" t="n">
+        <v>3.085E7</v>
+      </c>
+      <c r="P93" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q93" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="n">
+        <v>88.0</v>
+      </c>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C93" s="6" t="inlineStr">
+      <c r="C94" s="6" t="inlineStr">
         <is>
           <t>C26MYX</t>
         </is>
       </c>
-      <c r="D93" s="7" t="inlineStr">
+      <c r="D94" s="7" t="inlineStr">
         <is>
           <t>11088</t>
         </is>
       </c>
-      <c r="E93" s="7" t="inlineStr">
+      <c r="E94" s="7" t="inlineStr">
         <is>
           <t>09/09/2026</t>
         </is>
       </c>
-      <c r="F93" s="7" t="inlineStr">
+      <c r="F94" s="7" t="inlineStr">
         <is>
           <t>3502573440</t>
         </is>
       </c>
-      <c r="G93" s="6" t="inlineStr">
+      <c r="G94" s="6" t="inlineStr">
         <is>
           <t>Trạm Y tế phường Tam Thắng</t>
         </is>
       </c>
-      <c r="H93" s="6" t="inlineStr">
+      <c r="H94" s="6" t="inlineStr">
         <is>
           <t>số 278 Lê Lợi, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
-      <c r="I93" s="7" t="inlineStr">
-        <is>
-          <t>3502550210</t>
-        </is>
-      </c>
-      <c r="J93" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
-        </is>
-      </c>
-      <c r="K93" s="6"/>
-      <c r="L93" s="13"/>
-      <c r="M93" s="13"/>
-      <c r="N93" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O93" s="13" t="n">
+      <c r="I94" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J94" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K94" s="6"/>
+      <c r="L94" s="13"/>
+      <c r="M94" s="13"/>
+      <c r="N94" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O94" s="13" t="n">
         <v>2411000.0</v>
       </c>
-      <c r="P93" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q93" s="6" t="inlineStr">
+      <c r="P94" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q94" s="6" t="inlineStr">
         <is>
           <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
         </is>

--- a/Hoadon/HD2026/HDVao/9/3502550210_HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HD2026/HDVao/9/3502550210_HDDienTuMayTinhTien.xlsx
@@ -3873,32 +3873,32 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>C26MRT</t>
+          <t>C26MRV</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>19674</t>
+          <t>50506</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>3501013206</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI BẠCH MAI</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t>Số 01A Tô Nguyệt Đình, Phường Long Hương, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I57" s="7" t="inlineStr">
@@ -3913,16 +3913,16 @@
       </c>
       <c r="K57" s="6"/>
       <c r="L57" s="13" t="n">
-        <v>3944445.0</v>
+        <v>4110850.0</v>
       </c>
       <c r="M57" s="13" t="n">
-        <v>315555.0</v>
+        <v>328868.0</v>
       </c>
       <c r="N57" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O57" s="13" t="n">
-        <v>4260000.0</v>
+        <v>4439718.0</v>
       </c>
       <c r="P57" s="6" t="inlineStr">
         <is>
@@ -3951,12 +3951,12 @@
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>19874</t>
+          <t>19674</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
@@ -3986,16 +3986,16 @@
       </c>
       <c r="K58" s="6"/>
       <c r="L58" s="13" t="n">
-        <v>2425926.0</v>
+        <v>3944445.0</v>
       </c>
       <c r="M58" s="13" t="n">
-        <v>194074.0</v>
+        <v>315555.0</v>
       </c>
       <c r="N58" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O58" s="13" t="n">
-        <v>2620000.0</v>
+        <v>4260000.0</v>
       </c>
       <c r="P58" s="6" t="inlineStr">
         <is>
@@ -4019,32 +4019,32 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>C26MHD</t>
+          <t>C26MRT</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19874</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>3501663719</t>
+          <t>3501013206</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HẢI ĐOÀN</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI BẠCH MAI</t>
         </is>
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>Số 135 đường 2/9, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 01A Tô Nguyệt Đình, Phường Long Hương, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I59" s="7" t="inlineStr">
@@ -4059,16 +4059,16 @@
       </c>
       <c r="K59" s="6"/>
       <c r="L59" s="13" t="n">
-        <v>1.49E7</v>
+        <v>2425926.0</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>1192000.0</v>
+        <v>194074.0</v>
       </c>
       <c r="N59" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>1.6092E7</v>
+        <v>2620000.0</v>
       </c>
       <c r="P59" s="6" t="inlineStr">
         <is>
@@ -4092,32 +4092,32 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>C26MTP</t>
+          <t>C26MHD</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>10101</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>3501981599</t>
+          <t>3501663719</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI THỊNH PHÁT VN</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HẢI ĐOÀN</t>
         </is>
       </c>
       <c r="H60" s="6" t="inlineStr">
         <is>
-          <t>Số 138 Nguyễn Thiện Thuật, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 135 đường 2/9, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I60" s="7" t="inlineStr">
@@ -4127,21 +4127,21 @@
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
-          <t>Công ty TNHH Thạnh Hương Bến Đình</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K60" s="6"/>
       <c r="L60" s="13" t="n">
-        <v>4.0E7</v>
+        <v>1.49E7</v>
       </c>
       <c r="M60" s="13" t="n">
-        <v>4000000.0</v>
+        <v>1192000.0</v>
       </c>
       <c r="N60" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O60" s="13" t="n">
-        <v>4.4E7</v>
+        <v>1.6092E7</v>
       </c>
       <c r="P60" s="6" t="inlineStr">
         <is>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>C26MTK</t>
+          <t>C26MTP</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>3118</t>
+          <t>10101</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
@@ -4180,17 +4180,17 @@
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>3502242819</t>
+          <t>3501981599</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THOẠI KHANG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI THỊNH PHÁT VN</t>
         </is>
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>36 Trường Chinh, Khu phố Hải An, Xã Long Hải, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 138 Nguyễn Thiện Thuật, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I61" s="7" t="inlineStr">
@@ -4200,19 +4200,21 @@
       </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>Công ty TNHH Thạnh Hương Bến Đình</t>
         </is>
       </c>
       <c r="K61" s="6"/>
       <c r="L61" s="13" t="n">
-        <v>3.0345454E7</v>
+        <v>4.0E7</v>
       </c>
       <c r="M61" s="13" t="n">
-        <v>3034546.0</v>
-      </c>
-      <c r="N61" s="13"/>
+        <v>4000000.0</v>
+      </c>
+      <c r="N61" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="O61" s="13" t="n">
-        <v>3.338E7</v>
+        <v>4.4E7</v>
       </c>
       <c r="P61" s="6" t="inlineStr">
         <is>
@@ -4236,32 +4238,32 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>C26MTK</t>
+          <t>C26MTP</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>3183</t>
+          <t>10525</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>3502242819</t>
+          <t>3501981599</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THOẠI KHANG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI THỊNH PHÁT VN</t>
         </is>
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t>36 Trường Chinh, Khu phố Hải An, Xã Long Hải, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 138 Nguyễn Thiện Thuật, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I62" s="7" t="inlineStr">
@@ -4271,19 +4273,21 @@
       </c>
       <c r="J62" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>Công ty TNHH Thạnh Hương Bến Đình</t>
         </is>
       </c>
       <c r="K62" s="6"/>
       <c r="L62" s="13" t="n">
-        <v>1.8657408E7</v>
+        <v>4.7090909E7</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>1492592.0</v>
-      </c>
-      <c r="N62" s="13"/>
+        <v>4709091.0</v>
+      </c>
+      <c r="N62" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="O62" s="13" t="n">
-        <v>2.015E7</v>
+        <v>5.18E7</v>
       </c>
       <c r="P62" s="6" t="inlineStr">
         <is>
@@ -4307,32 +4311,32 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>C26MHT</t>
+          <t>C26MTK</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>6877</t>
+          <t>3118</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>3502324074</t>
+          <t>3502242819</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ HƯƠNG THỊNH PHÁT</t>
+          <t>CÔNG TY TNHH THOẠI KHANG</t>
         </is>
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>69 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>36 Trường Chinh, Khu phố Hải An, Xã Long Hải, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I63" s="7" t="inlineStr">
@@ -4347,16 +4351,14 @@
       </c>
       <c r="K63" s="6"/>
       <c r="L63" s="13" t="n">
-        <v>1.90232E8</v>
+        <v>3.0345454E7</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>1.90232E7</v>
-      </c>
-      <c r="N63" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>3034546.0</v>
+      </c>
+      <c r="N63" s="13"/>
       <c r="O63" s="13" t="n">
-        <v>2.092552E8</v>
+        <v>3.338E7</v>
       </c>
       <c r="P63" s="6" t="inlineStr">
         <is>
@@ -4380,32 +4382,32 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>C26MHT</t>
+          <t>C26MTK</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>7059</t>
+          <t>3183</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>3502324074</t>
+          <t>3502242819</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ HƯƠNG THỊNH PHÁT</t>
+          <t>CÔNG TY TNHH THOẠI KHANG</t>
         </is>
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
-          <t>69 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>36 Trường Chinh, Khu phố Hải An, Xã Long Hải, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I64" s="7" t="inlineStr">
@@ -4420,16 +4422,14 @@
       </c>
       <c r="K64" s="6"/>
       <c r="L64" s="13" t="n">
-        <v>2.3779E8</v>
+        <v>1.8657408E7</v>
       </c>
       <c r="M64" s="13" t="n">
-        <v>2.3779E7</v>
-      </c>
-      <c r="N64" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>1492592.0</v>
+      </c>
+      <c r="N64" s="13"/>
       <c r="O64" s="13" t="n">
-        <v>2.61569E8</v>
+        <v>2.015E7</v>
       </c>
       <c r="P64" s="6" t="inlineStr">
         <is>
@@ -4458,12 +4458,12 @@
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>7082</t>
+          <t>6877</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
@@ -4493,16 +4493,16 @@
       </c>
       <c r="K65" s="6"/>
       <c r="L65" s="13" t="n">
-        <v>2.85348E8</v>
+        <v>1.90232E8</v>
       </c>
       <c r="M65" s="13" t="n">
-        <v>2.85348E7</v>
+        <v>1.90232E7</v>
       </c>
       <c r="N65" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O65" s="13" t="n">
-        <v>3.138828E8</v>
+        <v>2.092552E8</v>
       </c>
       <c r="P65" s="6" t="inlineStr">
         <is>
@@ -4526,32 +4526,32 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>C26MTD</t>
+          <t>C26MHT</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>6120</t>
+          <t>7059</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>3502344144</t>
+          <t>3502324074</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ HƯƠNG THỊNH PHÁT</t>
         </is>
       </c>
       <c r="H66" s="6" t="inlineStr">
         <is>
-          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+          <t>69 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I66" s="7" t="inlineStr">
@@ -4566,16 +4566,16 @@
       </c>
       <c r="K66" s="6"/>
       <c r="L66" s="13" t="n">
-        <v>4.443182E7</v>
+        <v>2.3779E8</v>
       </c>
       <c r="M66" s="13" t="n">
-        <v>4443180.0</v>
+        <v>2.3779E7</v>
       </c>
       <c r="N66" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O66" s="13" t="n">
-        <v>4.8875E7</v>
+        <v>2.61569E8</v>
       </c>
       <c r="P66" s="6" t="inlineStr">
         <is>
@@ -4599,32 +4599,32 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>C26MTD</t>
+          <t>C26MHT</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>6128</t>
+          <t>7082</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>3502344144</t>
+          <t>3502324074</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ HƯƠNG THỊNH PHÁT</t>
         </is>
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+          <t>69 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I67" s="7" t="inlineStr">
@@ -4639,16 +4639,16 @@
       </c>
       <c r="K67" s="6"/>
       <c r="L67" s="13" t="n">
-        <v>2833333.0</v>
+        <v>2.85348E8</v>
       </c>
       <c r="M67" s="13" t="n">
-        <v>226667.0</v>
+        <v>2.85348E7</v>
       </c>
       <c r="N67" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O67" s="13" t="n">
-        <v>3060000.0</v>
+        <v>3.138828E8</v>
       </c>
       <c r="P67" s="6" t="inlineStr">
         <is>
@@ -4677,12 +4677,12 @@
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>6156</t>
+          <t>6120</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr">
@@ -4712,16 +4712,16 @@
       </c>
       <c r="K68" s="6"/>
       <c r="L68" s="13" t="n">
-        <v>2.7490909E7</v>
+        <v>4.443182E7</v>
       </c>
       <c r="M68" s="13" t="n">
-        <v>2749091.0</v>
+        <v>4443180.0</v>
       </c>
       <c r="N68" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O68" s="13" t="n">
-        <v>3.024E7</v>
+        <v>4.8875E7</v>
       </c>
       <c r="P68" s="6" t="inlineStr">
         <is>
@@ -4750,12 +4750,12 @@
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>6410</t>
+          <t>6128</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
@@ -4785,16 +4785,16 @@
       </c>
       <c r="K69" s="6"/>
       <c r="L69" s="13" t="n">
-        <v>1.9818182E7</v>
+        <v>2833333.0</v>
       </c>
       <c r="M69" s="13" t="n">
-        <v>1981818.0</v>
+        <v>226667.0</v>
       </c>
       <c r="N69" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O69" s="13" t="n">
-        <v>2.18E7</v>
+        <v>3060000.0</v>
       </c>
       <c r="P69" s="6" t="inlineStr">
         <is>
@@ -4823,12 +4823,12 @@
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>6430</t>
+          <t>6156</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">
@@ -4858,16 +4858,16 @@
       </c>
       <c r="K70" s="6"/>
       <c r="L70" s="13" t="n">
-        <v>6441499.0</v>
+        <v>2.7490909E7</v>
       </c>
       <c r="M70" s="13" t="n">
-        <v>583501.0</v>
+        <v>2749091.0</v>
       </c>
       <c r="N70" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O70" s="13" t="n">
-        <v>7025000.0</v>
+        <v>3.024E7</v>
       </c>
       <c r="P70" s="6" t="inlineStr">
         <is>
@@ -4896,12 +4896,12 @@
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>6526</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
@@ -4931,16 +4931,16 @@
       </c>
       <c r="K71" s="6"/>
       <c r="L71" s="13" t="n">
-        <v>2.0363636E7</v>
+        <v>1.9818182E7</v>
       </c>
       <c r="M71" s="13" t="n">
-        <v>2036364.0</v>
+        <v>1981818.0</v>
       </c>
       <c r="N71" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O71" s="13" t="n">
-        <v>2.24E7</v>
+        <v>2.18E7</v>
       </c>
       <c r="P71" s="6" t="inlineStr">
         <is>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>6564</t>
+          <t>6430</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="F72" s="7" t="inlineStr">
@@ -5004,16 +5004,16 @@
       </c>
       <c r="K72" s="6"/>
       <c r="L72" s="13" t="n">
-        <v>1.4706398E7</v>
+        <v>6441499.0</v>
       </c>
       <c r="M72" s="13" t="n">
-        <v>1403602.0</v>
+        <v>583501.0</v>
       </c>
       <c r="N72" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O72" s="13" t="n">
-        <v>1.611E7</v>
+        <v>7025000.0</v>
       </c>
       <c r="P72" s="6" t="inlineStr">
         <is>
@@ -5042,12 +5042,12 @@
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>6566</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr">
@@ -5077,16 +5077,16 @@
       </c>
       <c r="K73" s="6"/>
       <c r="L73" s="13" t="n">
-        <v>3789142.0</v>
+        <v>2.0363636E7</v>
       </c>
       <c r="M73" s="13" t="n">
-        <v>335858.0</v>
+        <v>2036364.0</v>
       </c>
       <c r="N73" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O73" s="13" t="n">
-        <v>4125000.0</v>
+        <v>2.24E7</v>
       </c>
       <c r="P73" s="6" t="inlineStr">
         <is>
@@ -5115,12 +5115,12 @@
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>6638</t>
+          <t>6564</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
@@ -5150,16 +5150,16 @@
       </c>
       <c r="K74" s="6"/>
       <c r="L74" s="13" t="n">
-        <v>3.7609091E7</v>
+        <v>1.4706398E7</v>
       </c>
       <c r="M74" s="13" t="n">
-        <v>3760909.0</v>
+        <v>1403602.0</v>
       </c>
       <c r="N74" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O74" s="13" t="n">
-        <v>4.137E7</v>
+        <v>1.611E7</v>
       </c>
       <c r="P74" s="6" t="inlineStr">
         <is>
@@ -5188,12 +5188,12 @@
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>6644</t>
+          <t>6566</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="F75" s="7" t="inlineStr">
@@ -5223,16 +5223,16 @@
       </c>
       <c r="K75" s="6"/>
       <c r="L75" s="13" t="n">
-        <v>3.2181818E7</v>
+        <v>3789142.0</v>
       </c>
       <c r="M75" s="13" t="n">
-        <v>3218182.0</v>
+        <v>335858.0</v>
       </c>
       <c r="N75" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O75" s="13" t="n">
-        <v>3.54E7</v>
+        <v>4125000.0</v>
       </c>
       <c r="P75" s="6" t="inlineStr">
         <is>
@@ -5261,12 +5261,12 @@
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>6790</t>
+          <t>6638</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr">
@@ -5296,16 +5296,16 @@
       </c>
       <c r="K76" s="6"/>
       <c r="L76" s="13" t="n">
-        <v>1.29545455E8</v>
+        <v>3.7609091E7</v>
       </c>
       <c r="M76" s="13" t="n">
-        <v>1.2954545E7</v>
+        <v>3760909.0</v>
       </c>
       <c r="N76" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O76" s="13" t="n">
-        <v>1.425E8</v>
+        <v>4.137E7</v>
       </c>
       <c r="P76" s="6" t="inlineStr">
         <is>
@@ -5334,12 +5334,12 @@
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>6845</t>
+          <t>6644</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr">
@@ -5369,16 +5369,16 @@
       </c>
       <c r="K77" s="6"/>
       <c r="L77" s="13" t="n">
-        <v>1.8690909E7</v>
+        <v>3.2181818E7</v>
       </c>
       <c r="M77" s="13" t="n">
-        <v>1869091.0</v>
+        <v>3218182.0</v>
       </c>
       <c r="N77" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O77" s="13" t="n">
-        <v>2.056E7</v>
+        <v>3.54E7</v>
       </c>
       <c r="P77" s="6" t="inlineStr">
         <is>
@@ -5402,32 +5402,32 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>C26MTT</t>
+          <t>C26MTD</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>1389</t>
+          <t>6790</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>3502425499</t>
+          <t>3502344144</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH NPP TOÀN THẮNG PH</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
         </is>
       </c>
       <c r="H78" s="6" t="inlineStr">
         <is>
-          <t>75/9/7 Phạm Hồng Thái, Phường Tam Thắng, Thành Phố Hồ Chí Minh</t>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I78" s="7" t="inlineStr">
@@ -5442,16 +5442,16 @@
       </c>
       <c r="K78" s="6"/>
       <c r="L78" s="13" t="n">
-        <v>4059260.0</v>
+        <v>1.29545455E8</v>
       </c>
       <c r="M78" s="13" t="n">
-        <v>324740.0</v>
+        <v>1.2954545E7</v>
       </c>
       <c r="N78" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O78" s="13" t="n">
-        <v>4384000.0</v>
+        <v>1.425E8</v>
       </c>
       <c r="P78" s="6" t="inlineStr">
         <is>
@@ -5475,32 +5475,32 @@
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>C26MTA</t>
+          <t>C26MTD</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>6845</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>3502426622</t>
+          <t>3502344144</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẢO ANH VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
         </is>
       </c>
       <c r="H79" s="6" t="inlineStr">
         <is>
-          <t>Tổ 12, ấp Phước Hưng, Xã Long Hải, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I79" s="7" t="inlineStr">
@@ -5515,16 +5515,16 @@
       </c>
       <c r="K79" s="6"/>
       <c r="L79" s="13" t="n">
-        <v>2.1348148E7</v>
+        <v>1.8690909E7</v>
       </c>
       <c r="M79" s="13" t="n">
-        <v>1707852.0</v>
+        <v>1869091.0</v>
       </c>
       <c r="N79" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O79" s="13" t="n">
-        <v>2.3056E7</v>
+        <v>2.056E7</v>
       </c>
       <c r="P79" s="6" t="inlineStr">
         <is>
@@ -5548,32 +5548,32 @@
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>C26MYY</t>
+          <t>C26MTT</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>10008</t>
+          <t>1389</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>3502474552</t>
+          <t>3502425499</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI TRỌNG GIANG</t>
+          <t>CÔNG TY TNHH NPP TOÀN THẮNG PH</t>
         </is>
       </c>
       <c r="H80" s="6" t="inlineStr">
         <is>
-          <t>B16 Khu Tái Định Cư 199 Lô Khu Nhà Ở Đồi 2, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>75/9/7 Phạm Hồng Thái, Phường Tam Thắng, Thành Phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I80" s="7" t="inlineStr">
@@ -5588,16 +5588,16 @@
       </c>
       <c r="K80" s="6"/>
       <c r="L80" s="13" t="n">
-        <v>2727274.0</v>
+        <v>4059260.0</v>
       </c>
       <c r="M80" s="13" t="n">
-        <v>272727.0</v>
+        <v>324740.0</v>
       </c>
       <c r="N80" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O80" s="13" t="n">
-        <v>3000001.0</v>
+        <v>4384000.0</v>
       </c>
       <c r="P80" s="6" t="inlineStr">
         <is>
@@ -5621,32 +5621,32 @@
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>C26MYY</t>
+          <t>C26MTA</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>9295</t>
+          <t>395</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>3502474552</t>
+          <t>3502426622</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI TRỌNG GIANG</t>
+          <t>CÔNG TY TNHH THẢO ANH VŨNG TÀU</t>
         </is>
       </c>
       <c r="H81" s="6" t="inlineStr">
         <is>
-          <t>B16 Khu Tái Định Cư 199 Lô Khu Nhà Ở Đồi 2, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>Tổ 12, ấp Phước Hưng, Xã Long Hải, TP Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I81" s="7" t="inlineStr">
@@ -5661,16 +5661,16 @@
       </c>
       <c r="K81" s="6"/>
       <c r="L81" s="13" t="n">
-        <v>2727274.0</v>
+        <v>2.1348148E7</v>
       </c>
       <c r="M81" s="13" t="n">
-        <v>272727.0</v>
+        <v>1707852.0</v>
       </c>
       <c r="N81" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O81" s="13" t="n">
-        <v>3000001.0</v>
+        <v>2.3056E7</v>
       </c>
       <c r="P81" s="6" t="inlineStr">
         <is>
@@ -5699,12 +5699,12 @@
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>9324</t>
+          <t>10008</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="F82" s="7" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>9523</t>
+          <t>9295</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr">
@@ -5845,27 +5845,27 @@
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>3870</t>
+          <t>9324</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="F84" s="7" t="inlineStr">
         <is>
-          <t>3502483525</t>
+          <t>3502474552</t>
         </is>
       </c>
       <c r="G84" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI ĐẠI Ý 79</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI TRỌNG GIANG</t>
         </is>
       </c>
       <c r="H84" s="6" t="inlineStr">
         <is>
-          <t>Số 22/18/29 đường Nam Kỳ Khởi Nghĩa, Phường Vũng Tàu, TP Hồ Chí Minh , Việt Nam</t>
+          <t>B16 Khu Tái Định Cư 199 Lô Khu Nhà Ở Đồi 2, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I84" s="7" t="inlineStr">
@@ -5875,21 +5875,21 @@
       </c>
       <c r="J84" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K84" s="6"/>
       <c r="L84" s="13" t="n">
-        <v>7.8272727E7</v>
+        <v>2727274.0</v>
       </c>
       <c r="M84" s="13" t="n">
-        <v>7827273.0</v>
+        <v>272727.0</v>
       </c>
       <c r="N84" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O84" s="13" t="n">
-        <v>8.61E7</v>
+        <v>3000001.0</v>
       </c>
       <c r="P84" s="6" t="inlineStr">
         <is>
@@ -5913,32 +5913,32 @@
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>C26MNL</t>
+          <t>C26MYY</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>2509</t>
+          <t>9523</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>3502547930</t>
+          <t>3502474552</t>
         </is>
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI TRỌNG GIANG</t>
         </is>
       </c>
       <c r="H85" s="6" t="inlineStr">
         <is>
-          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>B16 Khu Tái Định Cư 199 Lô Khu Nhà Ở Đồi 2, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I85" s="7" t="inlineStr">
@@ -5953,16 +5953,16 @@
       </c>
       <c r="K85" s="6"/>
       <c r="L85" s="13" t="n">
-        <v>4.2592593E7</v>
+        <v>2727274.0</v>
       </c>
       <c r="M85" s="13" t="n">
-        <v>3407407.0</v>
+        <v>272727.0</v>
       </c>
       <c r="N85" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O85" s="13" t="n">
-        <v>4.6E7</v>
+        <v>3000001.0</v>
       </c>
       <c r="P85" s="6" t="inlineStr">
         <is>
@@ -5986,32 +5986,32 @@
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>C26MNL</t>
+          <t>C26MYY</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>2515</t>
+          <t>3870</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="F86" s="7" t="inlineStr">
         <is>
-          <t>3502547930</t>
+          <t>3502483525</t>
         </is>
       </c>
       <c r="G86" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI ĐẠI Ý 79</t>
         </is>
       </c>
       <c r="H86" s="6" t="inlineStr">
         <is>
-          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 22/18/29 đường Nam Kỳ Khởi Nghĩa, Phường Vũng Tàu, TP Hồ Chí Minh , Việt Nam</t>
         </is>
       </c>
       <c r="I86" s="7" t="inlineStr">
@@ -6021,21 +6021,21 @@
       </c>
       <c r="J86" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K86" s="6"/>
       <c r="L86" s="13" t="n">
-        <v>1.5185185E7</v>
+        <v>7.8272727E7</v>
       </c>
       <c r="M86" s="13" t="n">
-        <v>1214815.0</v>
+        <v>7827273.0</v>
       </c>
       <c r="N86" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O86" s="13" t="n">
-        <v>1.64E7</v>
+        <v>8.61E7</v>
       </c>
       <c r="P86" s="6" t="inlineStr">
         <is>
@@ -6064,12 +6064,12 @@
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>2549</t>
+          <t>2509</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr">
@@ -6099,16 +6099,16 @@
       </c>
       <c r="K87" s="6"/>
       <c r="L87" s="13" t="n">
-        <v>3320000.0</v>
+        <v>4.2592593E7</v>
       </c>
       <c r="M87" s="13" t="n">
-        <v>265600.0</v>
+        <v>3407407.0</v>
       </c>
       <c r="N87" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O87" s="13" t="n">
-        <v>3585600.0</v>
+        <v>4.6E7</v>
       </c>
       <c r="P87" s="6" t="inlineStr">
         <is>
@@ -6137,12 +6137,12 @@
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>2643</t>
+          <t>2515</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="F88" s="7" t="inlineStr">
@@ -6172,16 +6172,16 @@
       </c>
       <c r="K88" s="6"/>
       <c r="L88" s="13" t="n">
-        <v>2.5833333E7</v>
+        <v>1.5185185E7</v>
       </c>
       <c r="M88" s="13" t="n">
-        <v>2066667.0</v>
+        <v>1214815.0</v>
       </c>
       <c r="N88" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O88" s="13" t="n">
-        <v>2.79E7</v>
+        <v>1.64E7</v>
       </c>
       <c r="P88" s="6" t="inlineStr">
         <is>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>2715</t>
+          <t>2549</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="F89" s="7" t="inlineStr">
@@ -6245,16 +6245,16 @@
       </c>
       <c r="K89" s="6"/>
       <c r="L89" s="13" t="n">
-        <v>9987037.0</v>
+        <v>3320000.0</v>
       </c>
       <c r="M89" s="13" t="n">
-        <v>798963.0</v>
+        <v>265600.0</v>
       </c>
       <c r="N89" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O89" s="13" t="n">
-        <v>1.0786E7</v>
+        <v>3585600.0</v>
       </c>
       <c r="P89" s="6" t="inlineStr">
         <is>
@@ -6283,12 +6283,12 @@
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>2643</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="F90" s="7" t="inlineStr">
@@ -6318,16 +6318,16 @@
       </c>
       <c r="K90" s="6"/>
       <c r="L90" s="13" t="n">
-        <v>1425926.0</v>
+        <v>2.5833333E7</v>
       </c>
       <c r="M90" s="13" t="n">
-        <v>114074.0</v>
+        <v>2066667.0</v>
       </c>
       <c r="N90" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O90" s="13" t="n">
-        <v>1540000.0</v>
+        <v>2.79E7</v>
       </c>
       <c r="P90" s="6" t="inlineStr">
         <is>
@@ -6356,12 +6356,12 @@
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>2772</t>
+          <t>2715</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr">
@@ -6391,16 +6391,16 @@
       </c>
       <c r="K91" s="6"/>
       <c r="L91" s="13" t="n">
-        <v>3796296.0</v>
+        <v>9987037.0</v>
       </c>
       <c r="M91" s="13" t="n">
-        <v>303704.0</v>
+        <v>798963.0</v>
       </c>
       <c r="N91" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O91" s="13" t="n">
-        <v>4100000.0</v>
+        <v>1.0786E7</v>
       </c>
       <c r="P91" s="6" t="inlineStr">
         <is>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>2813</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr">
@@ -6464,16 +6464,16 @@
       </c>
       <c r="K92" s="6"/>
       <c r="L92" s="13" t="n">
-        <v>2138889.0</v>
+        <v>1425926.0</v>
       </c>
       <c r="M92" s="13" t="n">
-        <v>171111.0</v>
+        <v>114074.0</v>
       </c>
       <c r="N92" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O92" s="13" t="n">
-        <v>2310000.0</v>
+        <v>1540000.0</v>
       </c>
       <c r="P92" s="6" t="inlineStr">
         <is>
@@ -6502,12 +6502,12 @@
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>2909</t>
+          <t>2772</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="F93" s="7" t="inlineStr">
@@ -6537,16 +6537,16 @@
       </c>
       <c r="K93" s="6"/>
       <c r="L93" s="13" t="n">
-        <v>2.8564815E7</v>
+        <v>3796296.0</v>
       </c>
       <c r="M93" s="13" t="n">
-        <v>2285185.0</v>
+        <v>303704.0</v>
       </c>
       <c r="N93" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O93" s="13" t="n">
-        <v>3.085E7</v>
+        <v>4100000.0</v>
       </c>
       <c r="P93" s="6" t="inlineStr">
         <is>
@@ -6565,64 +6565,210 @@
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>C26MNL</t>
+        </is>
+      </c>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>2813</t>
+        </is>
+      </c>
+      <c r="E94" s="7" t="inlineStr">
+        <is>
+          <t>19/09/2026</t>
+        </is>
+      </c>
+      <c r="F94" s="7" t="inlineStr">
+        <is>
+          <t>3502547930</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+        </is>
+      </c>
+      <c r="H94" s="6" t="inlineStr">
+        <is>
+          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I94" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J94" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K94" s="6"/>
+      <c r="L94" s="13" t="n">
+        <v>2138889.0</v>
+      </c>
+      <c r="M94" s="13" t="n">
+        <v>171111.0</v>
+      </c>
+      <c r="N94" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O94" s="13" t="n">
+        <v>2310000.0</v>
+      </c>
+      <c r="P94" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q94" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="n">
+        <v>89.0</v>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>C26MNL</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>2909</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>3502547930</t>
+        </is>
+      </c>
+      <c r="G95" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+        </is>
+      </c>
+      <c r="H95" s="6" t="inlineStr">
+        <is>
+          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I95" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J95" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K95" s="6"/>
+      <c r="L95" s="13" t="n">
+        <v>2.8564815E7</v>
+      </c>
+      <c r="M95" s="13" t="n">
+        <v>2285185.0</v>
+      </c>
+      <c r="N95" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O95" s="13" t="n">
+        <v>3.085E7</v>
+      </c>
+      <c r="P95" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q95" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="n">
+        <v>90.0</v>
+      </c>
+      <c r="B96" s="7" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C94" s="6" t="inlineStr">
+      <c r="C96" s="6" t="inlineStr">
         <is>
           <t>C26MYX</t>
         </is>
       </c>
-      <c r="D94" s="7" t="inlineStr">
+      <c r="D96" s="7" t="inlineStr">
         <is>
           <t>11088</t>
         </is>
       </c>
-      <c r="E94" s="7" t="inlineStr">
+      <c r="E96" s="7" t="inlineStr">
         <is>
           <t>09/09/2026</t>
         </is>
       </c>
-      <c r="F94" s="7" t="inlineStr">
+      <c r="F96" s="7" t="inlineStr">
         <is>
           <t>3502573440</t>
         </is>
       </c>
-      <c r="G94" s="6" t="inlineStr">
+      <c r="G96" s="6" t="inlineStr">
         <is>
           <t>Trạm Y tế phường Tam Thắng</t>
         </is>
       </c>
-      <c r="H94" s="6" t="inlineStr">
+      <c r="H96" s="6" t="inlineStr">
         <is>
           <t>số 278 Lê Lợi, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
-      <c r="I94" s="7" t="inlineStr">
-        <is>
-          <t>3502550210</t>
-        </is>
-      </c>
-      <c r="J94" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
-        </is>
-      </c>
-      <c r="K94" s="6"/>
-      <c r="L94" s="13"/>
-      <c r="M94" s="13"/>
-      <c r="N94" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O94" s="13" t="n">
+      <c r="I96" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J96" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K96" s="6"/>
+      <c r="L96" s="13"/>
+      <c r="M96" s="13"/>
+      <c r="N96" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O96" s="13" t="n">
         <v>2411000.0</v>
       </c>
-      <c r="P94" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q94" s="6" t="inlineStr">
+      <c r="P96" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q96" s="6" t="inlineStr">
         <is>
           <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
         </is>

--- a/Hoadon/HD2026/HDVao/9/3502550210_HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HD2026/HDVao/9/3502550210_HDDienTuMayTinhTien.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn mới</t>
+          <t>Hóa đơn đã bị thay thế</t>
         </is>
       </c>
       <c r="Q9" s="6" t="inlineStr">
@@ -528,32 +528,32 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>C26MTT</t>
+          <t>C26MTL</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>970</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>042166008663</t>
+          <t>036185005456</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH VĂN PHÒNG PHẨM NGUYỄN AN NINH</t>
+          <t>HỘ KINH DOANH THANH LAN - NGUYỄN TRUNG</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>81 Nguyễn An Ninh, Phường Vũng Tàu, TP Hồ Chí Minh</t>
+          <t>34/17 đường Bắc Sơn, Phường Phước Thắng, TP Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
@@ -573,11 +573,11 @@
         <v>0.0</v>
       </c>
       <c r="O10" s="13" t="n">
-        <v>1905000.0</v>
+        <v>1578000.0</v>
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn mới</t>
+          <t>Hóa đơn thay thế</t>
         </is>
       </c>
       <c r="Q10" s="6" t="inlineStr">
@@ -597,32 +597,32 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>C26MTS</t>
+          <t>C26MTT</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>874</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>042182000628</t>
+          <t>042166008663</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH NGUYỄN THỊ SONG</t>
+          <t>HỘ KINH DOANH VĂN PHÒNG PHẨM NGUYỄN AN NINH</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>1/16/15B Ngô Đức Kế, Phường Tam Thắng, TP - HCM</t>
+          <t>81 Nguyễn An Ninh, Phường Vũng Tàu, TP Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
@@ -642,7 +642,7 @@
         <v>0.0</v>
       </c>
       <c r="O11" s="13" t="n">
-        <v>4593000.0</v>
+        <v>1905000.0</v>
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
@@ -671,12 +671,12 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>127</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -711,7 +711,7 @@
         <v>0.0</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>7434720.0</v>
+        <v>4593000.0</v>
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
@@ -735,32 +735,32 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>C26MTT</t>
+          <t>C26MTS</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>131</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>051076001913</t>
+          <t>042182000628</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH CÀ PHÊ THÁI NGUYÊN</t>
+          <t>HỘ KINH DOANH NGUYỄN THỊ SONG</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Tổ 15 khu phố Hải Dinh, Phường Long Hương, Thành Phố Hồ Chí Minh, Việt Nam.</t>
+          <t>1/16/15B Ngô Đức Kế, Phường Tam Thắng, TP - HCM</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
@@ -780,7 +780,7 @@
         <v>0.0</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>4300000.0</v>
+        <v>7434720.0</v>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
@@ -809,12 +809,12 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>267</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -849,7 +849,7 @@
         <v>0.0</v>
       </c>
       <c r="O14" s="13" t="n">
-        <v>4400000.0</v>
+        <v>4300000.0</v>
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
@@ -878,12 +878,12 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>283</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -918,7 +918,7 @@
         <v>0.0</v>
       </c>
       <c r="O15" s="13" t="n">
-        <v>4300000.0</v>
+        <v>4400000.0</v>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
@@ -942,32 +942,32 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>C26MVH</t>
+          <t>C26MTT</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>290</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>051084000003</t>
+          <t>051076001913</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH HOÀNG VŨ</t>
+          <t>HỘ KINH DOANH CÀ PHÊ THÁI NGUYÊN</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>Thửa đất số 240, Tờ bản đồ số 166, ấp Bình Tiền 2, xã Đức Hoà, tỉnh Tây Ninh</t>
+          <t>Tổ 15 khu phố Hải Dinh, Phường Long Hương, Thành Phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
@@ -987,7 +987,7 @@
         <v>0.0</v>
       </c>
       <c r="O16" s="13" t="n">
-        <v>2600000.0</v>
+        <v>4300000.0</v>
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
@@ -1011,32 +1011,32 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>C26MTT</t>
+          <t>C26MVH</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>28</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>077082002684</t>
+          <t>051084000003</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH CỬA HÀNG HOÀI MINH ANH</t>
+          <t>HỘ KINH DOANH HOÀNG VŨ</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>Số 41Y, khu phố Long Phượng, Xã Long Điền, TP Hồ Chí Minh</t>
+          <t>Thửa đất số 240, Tờ bản đồ số 166, ấp Bình Tiền 2, xã Đức Hoà, tỉnh Tây Ninh</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
@@ -1056,7 +1056,7 @@
         <v>0.0</v>
       </c>
       <c r="O17" s="13" t="n">
-        <v>4857000.0</v>
+        <v>2600000.0</v>
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
@@ -1080,32 +1080,32 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>C26MHH</t>
+          <t>C26MTT</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>180</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>077195006087</t>
+          <t>077082002684</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH TẠP HOÁ HỒNG HẠNH</t>
+          <t>HỘ KINH DOANH CỬA HÀNG HOÀI MINH ANH</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>Khu TĐC khu phố Tây Hoà Long, Phường Tam Long, TP Hồ Chí Minh</t>
+          <t>Số 41Y, khu phố Long Phượng, Xã Long Điền, TP Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
@@ -1125,7 +1125,7 @@
         <v>0.0</v>
       </c>
       <c r="O18" s="13" t="n">
-        <v>1796400.0</v>
+        <v>4857000.0</v>
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>138</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -1194,7 +1194,7 @@
         <v>0.0</v>
       </c>
       <c r="O19" s="13" t="n">
-        <v>4391200.0</v>
+        <v>1796400.0</v>
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>139</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
@@ -1263,7 +1263,7 @@
         <v>0.0</v>
       </c>
       <c r="O20" s="13" t="n">
-        <v>3443100.0</v>
+        <v>4391200.0</v>
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>141</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
@@ -1332,7 +1332,7 @@
         <v>0.0</v>
       </c>
       <c r="O21" s="13" t="n">
-        <v>1347300.0</v>
+        <v>3443100.0</v>
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
@@ -1361,12 +1361,12 @@
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>142</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
@@ -1401,7 +1401,7 @@
         <v>0.0</v>
       </c>
       <c r="O22" s="13" t="n">
-        <v>2894200.0</v>
+        <v>1347300.0</v>
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
@@ -1430,12 +1430,12 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>147</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
@@ -1470,7 +1470,7 @@
         <v>0.0</v>
       </c>
       <c r="O23" s="13" t="n">
-        <v>1796400.0</v>
+        <v>2894200.0</v>
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
@@ -1494,32 +1494,32 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>C26MYY</t>
+          <t>C26MHH</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>151</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>077196000132</t>
+          <t>077195006087</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Minh Tuyền</t>
+          <t>HỘ KINH DOANH TẠP HOÁ HỒNG HẠNH</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>441/6/4 đường Trần Phú, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>Khu TĐC khu phố Tây Hoà Long, Phường Tam Long, TP Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
@@ -1539,7 +1539,7 @@
         <v>0.0</v>
       </c>
       <c r="O24" s="13" t="n">
-        <v>3250000.0</v>
+        <v>1796400.0</v>
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
@@ -1563,32 +1563,32 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>C26MYY</t>
+          <t>C26MHH</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>153</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>077196000132</t>
+          <t>077195006087</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Minh Tuyền</t>
+          <t>HỘ KINH DOANH TẠP HOÁ HỒNG HẠNH</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>441/6/4 đường Trần Phú, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>Khu TĐC khu phố Tây Hoà Long, Phường Tam Long, TP Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I25" s="7" t="inlineStr">
@@ -1608,7 +1608,7 @@
         <v>0.0</v>
       </c>
       <c r="O25" s="13" t="n">
-        <v>3535000.0</v>
+        <v>2894200.0</v>
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
@@ -1637,12 +1637,12 @@
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>124</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
@@ -1677,7 +1677,7 @@
         <v>0.0</v>
       </c>
       <c r="O26" s="13" t="n">
-        <v>2940000.0</v>
+        <v>3250000.0</v>
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
@@ -1706,12 +1706,12 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>128</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
@@ -1746,7 +1746,7 @@
         <v>0.0</v>
       </c>
       <c r="O27" s="13" t="n">
-        <v>3575000.0</v>
+        <v>3535000.0</v>
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
@@ -1770,32 +1770,32 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>C26MMM</t>
+          <t>C26MYY</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>130</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>079056002409</t>
+          <t>077196000132</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>Cường Hưng</t>
+          <t>Nguyễn Thị Minh Tuyền</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>390i, Nguyễn Duy, Phường Chánh Hưng, Hồ Chí Minh, Việt Nam</t>
+          <t>441/6/4 đường Trần Phú, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
@@ -1815,7 +1815,7 @@
         <v>0.0</v>
       </c>
       <c r="O28" s="13" t="n">
-        <v>3400000.0</v>
+        <v>2940000.0</v>
       </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
@@ -1839,32 +1839,32 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>C26MMM</t>
+          <t>C26MYY</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>133</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>079056002409</t>
+          <t>077196000132</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>Cường Hưng</t>
+          <t>Nguyễn Thị Minh Tuyền</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>390i, Nguyễn Duy, Phường Chánh Hưng, Hồ Chí Minh, Việt Nam</t>
+          <t>441/6/4 đường Trần Phú, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I29" s="7" t="inlineStr">
@@ -1884,7 +1884,7 @@
         <v>0.0</v>
       </c>
       <c r="O29" s="13" t="n">
-        <v>3400000.0</v>
+        <v>3575000.0</v>
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
@@ -1908,32 +1908,32 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>C26MMH</t>
+          <t>C26MMM</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>106</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>079078009688</t>
+          <t>079056002409</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH MẠNH HIẾU</t>
+          <t>Cường Hưng</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>606 Tân Kỳ Tân Quý, KP7, P.Bình Hưng Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>390i, Nguyễn Duy, Phường Chánh Hưng, Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
@@ -1949,9 +1949,11 @@
       <c r="K30" s="6"/>
       <c r="L30" s="13"/>
       <c r="M30" s="13"/>
-      <c r="N30" s="13"/>
+      <c r="N30" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="O30" s="13" t="n">
-        <v>3700000.0</v>
+        <v>3400000.0</v>
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
@@ -1970,37 +1972,37 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>C26MRV</t>
+          <t>C26MMM</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>46147</t>
+          <t>114</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>3500704465</t>
+          <t>079056002409</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+          <t>Cường Hưng</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>390i, Nguyễn Duy, Phường Chánh Hưng, Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I31" s="7" t="inlineStr">
@@ -2014,17 +2016,13 @@
         </is>
       </c>
       <c r="K31" s="6"/>
-      <c r="L31" s="13" t="n">
-        <v>9220370.0</v>
-      </c>
-      <c r="M31" s="13" t="n">
-        <v>737630.0</v>
-      </c>
+      <c r="L31" s="13"/>
+      <c r="M31" s="13"/>
       <c r="N31" s="13" t="n">
-        <v>484030.0</v>
+        <v>0.0</v>
       </c>
       <c r="O31" s="13" t="n">
-        <v>9958000.0</v>
+        <v>3400000.0</v>
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
@@ -2043,37 +2041,37 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>C26MRV</t>
+          <t>C26MMH</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>46241</t>
+          <t>320</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>3500704465</t>
+          <t>079078009688</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+          <t>HỘ KINH DOANH MẠNH HIẾU</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>606 Tân Kỳ Tân Quý, KP7, P.Bình Hưng Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I32" s="7" t="inlineStr">
@@ -2087,17 +2085,11 @@
         </is>
       </c>
       <c r="K32" s="6"/>
-      <c r="L32" s="13" t="n">
-        <v>1667270.0</v>
-      </c>
-      <c r="M32" s="13" t="n">
-        <v>133382.0</v>
-      </c>
-      <c r="N32" s="13" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="L32" s="13"/>
+      <c r="M32" s="13"/>
+      <c r="N32" s="13"/>
       <c r="O32" s="13" t="n">
-        <v>1800652.0</v>
+        <v>3700000.0</v>
       </c>
       <c r="P32" s="6" t="inlineStr">
         <is>
@@ -2126,12 +2118,12 @@
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>46293</t>
+          <t>46147</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
@@ -2161,16 +2153,16 @@
       </c>
       <c r="K33" s="6"/>
       <c r="L33" s="13" t="n">
-        <v>3740741.0</v>
+        <v>9220370.0</v>
       </c>
       <c r="M33" s="13" t="n">
-        <v>299259.0</v>
+        <v>737630.0</v>
       </c>
       <c r="N33" s="13" t="n">
-        <v>501259.0</v>
+        <v>484030.0</v>
       </c>
       <c r="O33" s="13" t="n">
-        <v>4040000.0</v>
+        <v>9958000.0</v>
       </c>
       <c r="P33" s="6" t="inlineStr">
         <is>
@@ -2199,12 +2191,12 @@
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>46700</t>
+          <t>46241</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
@@ -2234,16 +2226,16 @@
       </c>
       <c r="K34" s="6"/>
       <c r="L34" s="13" t="n">
-        <v>5728120.0</v>
+        <v>1667270.0</v>
       </c>
       <c r="M34" s="13" t="n">
-        <v>458250.0</v>
+        <v>133382.0</v>
       </c>
       <c r="N34" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O34" s="13" t="n">
-        <v>6186370.0</v>
+        <v>1800652.0</v>
       </c>
       <c r="P34" s="6" t="inlineStr">
         <is>
@@ -2272,12 +2264,12 @@
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>46701</t>
+          <t>46293</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
@@ -2307,16 +2299,16 @@
       </c>
       <c r="K35" s="6"/>
       <c r="L35" s="13" t="n">
-        <v>1321200.0</v>
+        <v>3740741.0</v>
       </c>
       <c r="M35" s="13" t="n">
-        <v>105696.0</v>
+        <v>299259.0</v>
       </c>
       <c r="N35" s="13" t="n">
-        <v>0.0</v>
+        <v>501259.0</v>
       </c>
       <c r="O35" s="13" t="n">
-        <v>1426896.0</v>
+        <v>4040000.0</v>
       </c>
       <c r="P35" s="6" t="inlineStr">
         <is>
@@ -2345,7 +2337,7 @@
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>46725</t>
+          <t>46700</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
@@ -2380,16 +2372,16 @@
       </c>
       <c r="K36" s="6"/>
       <c r="L36" s="13" t="n">
-        <v>3588000.0</v>
+        <v>5728120.0</v>
       </c>
       <c r="M36" s="13" t="n">
-        <v>287040.0</v>
+        <v>458250.0</v>
       </c>
       <c r="N36" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O36" s="13" t="n">
-        <v>3875040.0</v>
+        <v>6186370.0</v>
       </c>
       <c r="P36" s="6" t="inlineStr">
         <is>
@@ -2418,12 +2410,12 @@
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>47160</t>
+          <t>46701</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
@@ -2453,16 +2445,16 @@
       </c>
       <c r="K37" s="6"/>
       <c r="L37" s="13" t="n">
-        <v>2566442.0</v>
+        <v>1321200.0</v>
       </c>
       <c r="M37" s="13" t="n">
-        <v>205315.0</v>
+        <v>105696.0</v>
       </c>
       <c r="N37" s="13" t="n">
-        <v>28158.0</v>
+        <v>0.0</v>
       </c>
       <c r="O37" s="13" t="n">
-        <v>2771757.0</v>
+        <v>1426896.0</v>
       </c>
       <c r="P37" s="6" t="inlineStr">
         <is>
@@ -2491,12 +2483,12 @@
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>47161</t>
+          <t>46725</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
@@ -2526,16 +2518,16 @@
       </c>
       <c r="K38" s="6"/>
       <c r="L38" s="13" t="n">
-        <v>2527200.0</v>
+        <v>3588000.0</v>
       </c>
       <c r="M38" s="13" t="n">
-        <v>202176.0</v>
+        <v>287040.0</v>
       </c>
       <c r="N38" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O38" s="13" t="n">
-        <v>2729376.0</v>
+        <v>3875040.0</v>
       </c>
       <c r="P38" s="6" t="inlineStr">
         <is>
@@ -2564,12 +2556,12 @@
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>47417</t>
+          <t>47160</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
@@ -2599,16 +2591,16 @@
       </c>
       <c r="K39" s="6"/>
       <c r="L39" s="13" t="n">
-        <v>2214900.0</v>
+        <v>2566442.0</v>
       </c>
       <c r="M39" s="13" t="n">
-        <v>177192.0</v>
+        <v>205315.0</v>
       </c>
       <c r="N39" s="13" t="n">
-        <v>0.0</v>
+        <v>28158.0</v>
       </c>
       <c r="O39" s="13" t="n">
-        <v>2392092.0</v>
+        <v>2771757.0</v>
       </c>
       <c r="P39" s="6" t="inlineStr">
         <is>
@@ -2637,12 +2629,12 @@
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>47657</t>
+          <t>47161</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
@@ -2672,16 +2664,16 @@
       </c>
       <c r="K40" s="6"/>
       <c r="L40" s="13" t="n">
-        <v>2512226.0</v>
+        <v>2527200.0</v>
       </c>
       <c r="M40" s="13" t="n">
-        <v>200978.0</v>
+        <v>202176.0</v>
       </c>
       <c r="N40" s="13" t="n">
-        <v>124874.0</v>
+        <v>0.0</v>
       </c>
       <c r="O40" s="13" t="n">
-        <v>2713204.0</v>
+        <v>2729376.0</v>
       </c>
       <c r="P40" s="6" t="inlineStr">
         <is>
@@ -2710,12 +2702,12 @@
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>47674</t>
+          <t>47417</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
@@ -2745,16 +2737,16 @@
       </c>
       <c r="K41" s="6"/>
       <c r="L41" s="13" t="n">
-        <v>3304000.0</v>
+        <v>2214900.0</v>
       </c>
       <c r="M41" s="13" t="n">
-        <v>264320.0</v>
+        <v>177192.0</v>
       </c>
       <c r="N41" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O41" s="13" t="n">
-        <v>3568320.0</v>
+        <v>2392092.0</v>
       </c>
       <c r="P41" s="6" t="inlineStr">
         <is>
@@ -2783,12 +2775,12 @@
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>47747</t>
+          <t>47657</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
@@ -2818,16 +2810,16 @@
       </c>
       <c r="K42" s="6"/>
       <c r="L42" s="13" t="n">
-        <v>3.8462963E7</v>
+        <v>2512226.0</v>
       </c>
       <c r="M42" s="13" t="n">
-        <v>3077037.0</v>
+        <v>200978.0</v>
       </c>
       <c r="N42" s="13" t="n">
-        <v>2559037.0</v>
+        <v>124874.0</v>
       </c>
       <c r="O42" s="13" t="n">
-        <v>4.154E7</v>
+        <v>2713204.0</v>
       </c>
       <c r="P42" s="6" t="inlineStr">
         <is>
@@ -2856,12 +2848,12 @@
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>48032</t>
+          <t>47674</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
@@ -2891,16 +2883,16 @@
       </c>
       <c r="K43" s="6"/>
       <c r="L43" s="13" t="n">
-        <v>2982590.0</v>
+        <v>3304000.0</v>
       </c>
       <c r="M43" s="13" t="n">
-        <v>238607.0</v>
+        <v>264320.0</v>
       </c>
       <c r="N43" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O43" s="13" t="n">
-        <v>3221197.0</v>
+        <v>3568320.0</v>
       </c>
       <c r="P43" s="6" t="inlineStr">
         <is>
@@ -2929,12 +2921,12 @@
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>48441</t>
+          <t>47747</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
@@ -2964,16 +2956,16 @@
       </c>
       <c r="K44" s="6"/>
       <c r="L44" s="13" t="n">
-        <v>4676000.0</v>
+        <v>3.8462963E7</v>
       </c>
       <c r="M44" s="13" t="n">
-        <v>374080.0</v>
+        <v>3077037.0</v>
       </c>
       <c r="N44" s="13" t="n">
-        <v>0.0</v>
+        <v>2559037.0</v>
       </c>
       <c r="O44" s="13" t="n">
-        <v>5050080.0</v>
+        <v>4.154E7</v>
       </c>
       <c r="P44" s="6" t="inlineStr">
         <is>
@@ -3002,12 +2994,12 @@
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>48442</t>
+          <t>48032</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
@@ -3037,16 +3029,16 @@
       </c>
       <c r="K45" s="6"/>
       <c r="L45" s="13" t="n">
-        <v>5013650.0</v>
+        <v>2982590.0</v>
       </c>
       <c r="M45" s="13" t="n">
-        <v>401092.0</v>
+        <v>238607.0</v>
       </c>
       <c r="N45" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O45" s="13" t="n">
-        <v>5414742.0</v>
+        <v>3221197.0</v>
       </c>
       <c r="P45" s="6" t="inlineStr">
         <is>
@@ -3075,12 +3067,12 @@
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>48834</t>
+          <t>48441</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
@@ -3110,16 +3102,16 @@
       </c>
       <c r="K46" s="6"/>
       <c r="L46" s="13" t="n">
-        <v>2238242.0</v>
+        <v>4676000.0</v>
       </c>
       <c r="M46" s="13" t="n">
-        <v>179059.0</v>
+        <v>374080.0</v>
       </c>
       <c r="N46" s="13" t="n">
-        <v>28158.0</v>
+        <v>0.0</v>
       </c>
       <c r="O46" s="13" t="n">
-        <v>2417301.0</v>
+        <v>5050080.0</v>
       </c>
       <c r="P46" s="6" t="inlineStr">
         <is>
@@ -3148,12 +3140,12 @@
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>49247</t>
+          <t>48442</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
@@ -3183,16 +3175,16 @@
       </c>
       <c r="K47" s="6"/>
       <c r="L47" s="13" t="n">
-        <v>2208000.0</v>
+        <v>5013650.0</v>
       </c>
       <c r="M47" s="13" t="n">
-        <v>176640.0</v>
+        <v>401092.0</v>
       </c>
       <c r="N47" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O47" s="13" t="n">
-        <v>2384640.0</v>
+        <v>5414742.0</v>
       </c>
       <c r="P47" s="6" t="inlineStr">
         <is>
@@ -3221,12 +3213,12 @@
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>49424</t>
+          <t>48834</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
@@ -3256,16 +3248,16 @@
       </c>
       <c r="K48" s="6"/>
       <c r="L48" s="13" t="n">
-        <v>4488889.0</v>
+        <v>2238242.0</v>
       </c>
       <c r="M48" s="13" t="n">
-        <v>359111.0</v>
+        <v>179059.0</v>
       </c>
       <c r="N48" s="13" t="n">
-        <v>601511.0</v>
+        <v>28158.0</v>
       </c>
       <c r="O48" s="13" t="n">
-        <v>4848000.0</v>
+        <v>2417301.0</v>
       </c>
       <c r="P48" s="6" t="inlineStr">
         <is>
@@ -3294,12 +3286,12 @@
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>49427</t>
+          <t>49247</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
@@ -3329,16 +3321,16 @@
       </c>
       <c r="K49" s="6"/>
       <c r="L49" s="13" t="n">
-        <v>0.0</v>
+        <v>2208000.0</v>
       </c>
       <c r="M49" s="13" t="n">
-        <v>0.0</v>
+        <v>176640.0</v>
       </c>
       <c r="N49" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O49" s="13" t="n">
-        <v>0.0</v>
+        <v>2384640.0</v>
       </c>
       <c r="P49" s="6" t="inlineStr">
         <is>
@@ -3367,7 +3359,7 @@
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>49491</t>
+          <t>49424</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
@@ -3402,16 +3394,16 @@
       </c>
       <c r="K50" s="6"/>
       <c r="L50" s="13" t="n">
-        <v>660700.0</v>
+        <v>4488889.0</v>
       </c>
       <c r="M50" s="13" t="n">
-        <v>52856.0</v>
+        <v>359111.0</v>
       </c>
       <c r="N50" s="13" t="n">
-        <v>0.0</v>
+        <v>601511.0</v>
       </c>
       <c r="O50" s="13" t="n">
-        <v>713556.0</v>
+        <v>4848000.0</v>
       </c>
       <c r="P50" s="6" t="inlineStr">
         <is>
@@ -3440,7 +3432,7 @@
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>49492</t>
+          <t>49427</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
@@ -3475,16 +3467,16 @@
       </c>
       <c r="K51" s="6"/>
       <c r="L51" s="13" t="n">
-        <v>1800739.0</v>
+        <v>0.0</v>
       </c>
       <c r="M51" s="13" t="n">
-        <v>144059.0</v>
+        <v>0.0</v>
       </c>
       <c r="N51" s="13" t="n">
-        <v>83761.0</v>
+        <v>0.0</v>
       </c>
       <c r="O51" s="13" t="n">
-        <v>1944798.0</v>
+        <v>0.0</v>
       </c>
       <c r="P51" s="6" t="inlineStr">
         <is>
@@ -3513,12 +3505,12 @@
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>49563</t>
+          <t>49491</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
@@ -3548,16 +3540,16 @@
       </c>
       <c r="K52" s="6"/>
       <c r="L52" s="13" t="n">
-        <v>959044.0</v>
+        <v>660700.0</v>
       </c>
       <c r="M52" s="13" t="n">
-        <v>76724.0</v>
+        <v>52856.0</v>
       </c>
       <c r="N52" s="13" t="n">
-        <v>106556.0</v>
+        <v>0.0</v>
       </c>
       <c r="O52" s="13" t="n">
-        <v>1035768.0</v>
+        <v>713556.0</v>
       </c>
       <c r="P52" s="6" t="inlineStr">
         <is>
@@ -3586,12 +3578,12 @@
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>49664</t>
+          <t>49492</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
@@ -3621,16 +3613,16 @@
       </c>
       <c r="K53" s="6"/>
       <c r="L53" s="13" t="n">
-        <v>5654100.0</v>
+        <v>1800739.0</v>
       </c>
       <c r="M53" s="13" t="n">
-        <v>452328.0</v>
+        <v>144059.0</v>
       </c>
       <c r="N53" s="13" t="n">
-        <v>0.0</v>
+        <v>83761.0</v>
       </c>
       <c r="O53" s="13" t="n">
-        <v>6106428.0</v>
+        <v>1944798.0</v>
       </c>
       <c r="P53" s="6" t="inlineStr">
         <is>
@@ -3659,7 +3651,7 @@
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>49665</t>
+          <t>49563</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
@@ -3694,16 +3686,16 @@
       </c>
       <c r="K54" s="6"/>
       <c r="L54" s="13" t="n">
-        <v>1476000.0</v>
+        <v>959044.0</v>
       </c>
       <c r="M54" s="13" t="n">
-        <v>118080.0</v>
+        <v>76724.0</v>
       </c>
       <c r="N54" s="13" t="n">
-        <v>0.0</v>
+        <v>106556.0</v>
       </c>
       <c r="O54" s="13" t="n">
-        <v>1594080.0</v>
+        <v>1035768.0</v>
       </c>
       <c r="P54" s="6" t="inlineStr">
         <is>
@@ -3732,12 +3724,12 @@
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>49891</t>
+          <t>49664</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
@@ -3767,16 +3759,16 @@
       </c>
       <c r="K55" s="6"/>
       <c r="L55" s="13" t="n">
-        <v>5040220.0</v>
+        <v>5654100.0</v>
       </c>
       <c r="M55" s="13" t="n">
-        <v>403218.0</v>
+        <v>452328.0</v>
       </c>
       <c r="N55" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O55" s="13" t="n">
-        <v>5443438.0</v>
+        <v>6106428.0</v>
       </c>
       <c r="P55" s="6" t="inlineStr">
         <is>
@@ -3805,12 +3797,12 @@
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>50131</t>
+          <t>49665</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
@@ -3840,16 +3832,16 @@
       </c>
       <c r="K56" s="6"/>
       <c r="L56" s="13" t="n">
-        <v>708294.0</v>
+        <v>1476000.0</v>
       </c>
       <c r="M56" s="13" t="n">
-        <v>56664.0</v>
+        <v>118080.0</v>
       </c>
       <c r="N56" s="13" t="n">
-        <v>21906.0</v>
+        <v>0.0</v>
       </c>
       <c r="O56" s="13" t="n">
-        <v>764958.0</v>
+        <v>1594080.0</v>
       </c>
       <c r="P56" s="6" t="inlineStr">
         <is>
@@ -3878,12 +3870,12 @@
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>50506</t>
+          <t>49891</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
@@ -3913,16 +3905,16 @@
       </c>
       <c r="K57" s="6"/>
       <c r="L57" s="13" t="n">
-        <v>4110850.0</v>
+        <v>5040220.0</v>
       </c>
       <c r="M57" s="13" t="n">
-        <v>328868.0</v>
+        <v>403218.0</v>
       </c>
       <c r="N57" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O57" s="13" t="n">
-        <v>4439718.0</v>
+        <v>5443438.0</v>
       </c>
       <c r="P57" s="6" t="inlineStr">
         <is>
@@ -3946,32 +3938,32 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>C26MRT</t>
+          <t>C26MRV</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>19674</t>
+          <t>50131</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>3501013206</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI BẠCH MAI</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>Số 01A Tô Nguyệt Đình, Phường Long Hương, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I58" s="7" t="inlineStr">
@@ -3986,16 +3978,16 @@
       </c>
       <c r="K58" s="6"/>
       <c r="L58" s="13" t="n">
-        <v>3944445.0</v>
+        <v>708294.0</v>
       </c>
       <c r="M58" s="13" t="n">
-        <v>315555.0</v>
+        <v>56664.0</v>
       </c>
       <c r="N58" s="13" t="n">
-        <v>0.0</v>
+        <v>21906.0</v>
       </c>
       <c r="O58" s="13" t="n">
-        <v>4260000.0</v>
+        <v>764958.0</v>
       </c>
       <c r="P58" s="6" t="inlineStr">
         <is>
@@ -4019,32 +4011,32 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>C26MRT</t>
+          <t>C26MRV</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>19874</t>
+          <t>50506</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>3501013206</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI BẠCH MAI</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>Số 01A Tô Nguyệt Đình, Phường Long Hương, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I59" s="7" t="inlineStr">
@@ -4059,16 +4051,16 @@
       </c>
       <c r="K59" s="6"/>
       <c r="L59" s="13" t="n">
-        <v>2425926.0</v>
+        <v>4110850.0</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>194074.0</v>
+        <v>328868.0</v>
       </c>
       <c r="N59" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>2620000.0</v>
+        <v>4439718.0</v>
       </c>
       <c r="P59" s="6" t="inlineStr">
         <is>
@@ -4092,12 +4084,12 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>C26MHD</t>
+          <t>C26MRT</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19674</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
@@ -4107,17 +4099,17 @@
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>3501663719</t>
+          <t>3501013206</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HẢI ĐOÀN</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI BẠCH MAI</t>
         </is>
       </c>
       <c r="H60" s="6" t="inlineStr">
         <is>
-          <t>Số 135 đường 2/9, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 01A Tô Nguyệt Đình, Phường Long Hương, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I60" s="7" t="inlineStr">
@@ -4132,16 +4124,16 @@
       </c>
       <c r="K60" s="6"/>
       <c r="L60" s="13" t="n">
-        <v>1.49E7</v>
+        <v>3944445.0</v>
       </c>
       <c r="M60" s="13" t="n">
-        <v>1192000.0</v>
+        <v>315555.0</v>
       </c>
       <c r="N60" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O60" s="13" t="n">
-        <v>1.6092E7</v>
+        <v>4260000.0</v>
       </c>
       <c r="P60" s="6" t="inlineStr">
         <is>
@@ -4165,32 +4157,32 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>C26MTP</t>
+          <t>C26MRT</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>10101</t>
+          <t>19874</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>3501981599</t>
+          <t>3501013206</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI THỊNH PHÁT VN</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI BẠCH MAI</t>
         </is>
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>Số 138 Nguyễn Thiện Thuật, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 01A Tô Nguyệt Đình, Phường Long Hương, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I61" s="7" t="inlineStr">
@@ -4200,21 +4192,21 @@
       </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
-          <t>Công ty TNHH Thạnh Hương Bến Đình</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K61" s="6"/>
       <c r="L61" s="13" t="n">
-        <v>4.0E7</v>
+        <v>2425926.0</v>
       </c>
       <c r="M61" s="13" t="n">
-        <v>4000000.0</v>
+        <v>194074.0</v>
       </c>
       <c r="N61" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O61" s="13" t="n">
-        <v>4.4E7</v>
+        <v>2620000.0</v>
       </c>
       <c r="P61" s="6" t="inlineStr">
         <is>
@@ -4238,32 +4230,32 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>C26MTP</t>
+          <t>C26MHD</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>10525</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>3501981599</t>
+          <t>3501663719</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI THỊNH PHÁT VN</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HẢI ĐOÀN</t>
         </is>
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t>Số 138 Nguyễn Thiện Thuật, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 135 đường 2/9, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I62" s="7" t="inlineStr">
@@ -4273,21 +4265,21 @@
       </c>
       <c r="J62" s="6" t="inlineStr">
         <is>
-          <t>Công ty TNHH Thạnh Hương Bến Đình</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K62" s="6"/>
       <c r="L62" s="13" t="n">
-        <v>4.7090909E7</v>
+        <v>1.49E7</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>4709091.0</v>
+        <v>1192000.0</v>
       </c>
       <c r="N62" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>5.18E7</v>
+        <v>1.6092E7</v>
       </c>
       <c r="P62" s="6" t="inlineStr">
         <is>
@@ -4311,12 +4303,12 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>C26MTK</t>
+          <t>C26MTP</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>3118</t>
+          <t>10101</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
@@ -4326,17 +4318,17 @@
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>3502242819</t>
+          <t>3501981599</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THOẠI KHANG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI THỊNH PHÁT VN</t>
         </is>
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>36 Trường Chinh, Khu phố Hải An, Xã Long Hải, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 138 Nguyễn Thiện Thuật, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I63" s="7" t="inlineStr">
@@ -4346,19 +4338,21 @@
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>Công ty TNHH Thạnh Hương Bến Đình</t>
         </is>
       </c>
       <c r="K63" s="6"/>
       <c r="L63" s="13" t="n">
-        <v>3.0345454E7</v>
+        <v>4.0E7</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>3034546.0</v>
-      </c>
-      <c r="N63" s="13"/>
+        <v>4000000.0</v>
+      </c>
+      <c r="N63" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="O63" s="13" t="n">
-        <v>3.338E7</v>
+        <v>4.4E7</v>
       </c>
       <c r="P63" s="6" t="inlineStr">
         <is>
@@ -4382,32 +4376,32 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>C26MTK</t>
+          <t>C26MTP</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>3183</t>
+          <t>10525</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>3502242819</t>
+          <t>3501981599</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THOẠI KHANG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI THỊNH PHÁT VN</t>
         </is>
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
-          <t>36 Trường Chinh, Khu phố Hải An, Xã Long Hải, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 138 Nguyễn Thiện Thuật, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I64" s="7" t="inlineStr">
@@ -4417,19 +4411,21 @@
       </c>
       <c r="J64" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>Công ty TNHH Thạnh Hương Bến Đình</t>
         </is>
       </c>
       <c r="K64" s="6"/>
       <c r="L64" s="13" t="n">
-        <v>1.8657408E7</v>
+        <v>4.7090909E7</v>
       </c>
       <c r="M64" s="13" t="n">
-        <v>1492592.0</v>
-      </c>
-      <c r="N64" s="13"/>
+        <v>4709091.0</v>
+      </c>
+      <c r="N64" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="O64" s="13" t="n">
-        <v>2.015E7</v>
+        <v>5.18E7</v>
       </c>
       <c r="P64" s="6" t="inlineStr">
         <is>
@@ -4453,32 +4449,32 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>C26MHT</t>
+          <t>C26MTK</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>6877</t>
+          <t>3118</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>3502324074</t>
+          <t>3502242819</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ HƯƠNG THỊNH PHÁT</t>
+          <t>CÔNG TY TNHH THOẠI KHANG</t>
         </is>
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>69 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>36 Trường Chinh, Khu phố Hải An, Xã Long Hải, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I65" s="7" t="inlineStr">
@@ -4493,16 +4489,14 @@
       </c>
       <c r="K65" s="6"/>
       <c r="L65" s="13" t="n">
-        <v>1.90232E8</v>
+        <v>3.0345454E7</v>
       </c>
       <c r="M65" s="13" t="n">
-        <v>1.90232E7</v>
-      </c>
-      <c r="N65" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>3034546.0</v>
+      </c>
+      <c r="N65" s="13"/>
       <c r="O65" s="13" t="n">
-        <v>2.092552E8</v>
+        <v>3.338E7</v>
       </c>
       <c r="P65" s="6" t="inlineStr">
         <is>
@@ -4526,32 +4520,32 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>C26MHT</t>
+          <t>C26MTK</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>7059</t>
+          <t>3183</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>3502324074</t>
+          <t>3502242819</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ HƯƠNG THỊNH PHÁT</t>
+          <t>CÔNG TY TNHH THOẠI KHANG</t>
         </is>
       </c>
       <c r="H66" s="6" t="inlineStr">
         <is>
-          <t>69 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>36 Trường Chinh, Khu phố Hải An, Xã Long Hải, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I66" s="7" t="inlineStr">
@@ -4566,16 +4560,14 @@
       </c>
       <c r="K66" s="6"/>
       <c r="L66" s="13" t="n">
-        <v>2.3779E8</v>
+        <v>1.8657408E7</v>
       </c>
       <c r="M66" s="13" t="n">
-        <v>2.3779E7</v>
-      </c>
-      <c r="N66" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>1492592.0</v>
+      </c>
+      <c r="N66" s="13"/>
       <c r="O66" s="13" t="n">
-        <v>2.61569E8</v>
+        <v>2.015E7</v>
       </c>
       <c r="P66" s="6" t="inlineStr">
         <is>
@@ -4604,12 +4596,12 @@
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>7082</t>
+          <t>6877</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
@@ -4639,16 +4631,16 @@
       </c>
       <c r="K67" s="6"/>
       <c r="L67" s="13" t="n">
-        <v>2.85348E8</v>
+        <v>1.90232E8</v>
       </c>
       <c r="M67" s="13" t="n">
-        <v>2.85348E7</v>
+        <v>1.90232E7</v>
       </c>
       <c r="N67" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O67" s="13" t="n">
-        <v>3.138828E8</v>
+        <v>2.092552E8</v>
       </c>
       <c r="P67" s="6" t="inlineStr">
         <is>
@@ -4672,32 +4664,32 @@
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>C26MTD</t>
+          <t>C26MHT</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>6120</t>
+          <t>7059</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>3502344144</t>
+          <t>3502324074</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ HƯƠNG THỊNH PHÁT</t>
         </is>
       </c>
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+          <t>69 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I68" s="7" t="inlineStr">
@@ -4712,16 +4704,16 @@
       </c>
       <c r="K68" s="6"/>
       <c r="L68" s="13" t="n">
-        <v>4.443182E7</v>
+        <v>2.3779E8</v>
       </c>
       <c r="M68" s="13" t="n">
-        <v>4443180.0</v>
+        <v>2.3779E7</v>
       </c>
       <c r="N68" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O68" s="13" t="n">
-        <v>4.8875E7</v>
+        <v>2.61569E8</v>
       </c>
       <c r="P68" s="6" t="inlineStr">
         <is>
@@ -4745,32 +4737,32 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>C26MTD</t>
+          <t>C26MHT</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>6128</t>
+          <t>7082</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>3502344144</t>
+          <t>3502324074</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ HƯƠNG THỊNH PHÁT</t>
         </is>
       </c>
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+          <t>69 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I69" s="7" t="inlineStr">
@@ -4785,16 +4777,16 @@
       </c>
       <c r="K69" s="6"/>
       <c r="L69" s="13" t="n">
-        <v>2833333.0</v>
+        <v>2.85348E8</v>
       </c>
       <c r="M69" s="13" t="n">
-        <v>226667.0</v>
+        <v>2.85348E7</v>
       </c>
       <c r="N69" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O69" s="13" t="n">
-        <v>3060000.0</v>
+        <v>3.138828E8</v>
       </c>
       <c r="P69" s="6" t="inlineStr">
         <is>
@@ -4823,12 +4815,12 @@
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>6156</t>
+          <t>6120</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">
@@ -4858,16 +4850,16 @@
       </c>
       <c r="K70" s="6"/>
       <c r="L70" s="13" t="n">
-        <v>2.7490909E7</v>
+        <v>4.443182E7</v>
       </c>
       <c r="M70" s="13" t="n">
-        <v>2749091.0</v>
+        <v>4443180.0</v>
       </c>
       <c r="N70" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O70" s="13" t="n">
-        <v>3.024E7</v>
+        <v>4.8875E7</v>
       </c>
       <c r="P70" s="6" t="inlineStr">
         <is>
@@ -4896,12 +4888,12 @@
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>6410</t>
+          <t>6128</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
@@ -4931,16 +4923,16 @@
       </c>
       <c r="K71" s="6"/>
       <c r="L71" s="13" t="n">
-        <v>1.9818182E7</v>
+        <v>2833333.0</v>
       </c>
       <c r="M71" s="13" t="n">
-        <v>1981818.0</v>
+        <v>226667.0</v>
       </c>
       <c r="N71" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O71" s="13" t="n">
-        <v>2.18E7</v>
+        <v>3060000.0</v>
       </c>
       <c r="P71" s="6" t="inlineStr">
         <is>
@@ -4969,12 +4961,12 @@
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>6430</t>
+          <t>6156</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="F72" s="7" t="inlineStr">
@@ -5004,16 +4996,16 @@
       </c>
       <c r="K72" s="6"/>
       <c r="L72" s="13" t="n">
-        <v>6441499.0</v>
+        <v>2.7490909E7</v>
       </c>
       <c r="M72" s="13" t="n">
-        <v>583501.0</v>
+        <v>2749091.0</v>
       </c>
       <c r="N72" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O72" s="13" t="n">
-        <v>7025000.0</v>
+        <v>3.024E7</v>
       </c>
       <c r="P72" s="6" t="inlineStr">
         <is>
@@ -5042,12 +5034,12 @@
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>6526</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr">
@@ -5077,16 +5069,16 @@
       </c>
       <c r="K73" s="6"/>
       <c r="L73" s="13" t="n">
-        <v>2.0363636E7</v>
+        <v>1.9818182E7</v>
       </c>
       <c r="M73" s="13" t="n">
-        <v>2036364.0</v>
+        <v>1981818.0</v>
       </c>
       <c r="N73" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O73" s="13" t="n">
-        <v>2.24E7</v>
+        <v>2.18E7</v>
       </c>
       <c r="P73" s="6" t="inlineStr">
         <is>
@@ -5115,12 +5107,12 @@
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>6564</t>
+          <t>6430</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
@@ -5150,16 +5142,16 @@
       </c>
       <c r="K74" s="6"/>
       <c r="L74" s="13" t="n">
-        <v>1.4706398E7</v>
+        <v>6441499.0</v>
       </c>
       <c r="M74" s="13" t="n">
-        <v>1403602.0</v>
+        <v>583501.0</v>
       </c>
       <c r="N74" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O74" s="13" t="n">
-        <v>1.611E7</v>
+        <v>7025000.0</v>
       </c>
       <c r="P74" s="6" t="inlineStr">
         <is>
@@ -5188,12 +5180,12 @@
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>6566</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="F75" s="7" t="inlineStr">
@@ -5223,16 +5215,16 @@
       </c>
       <c r="K75" s="6"/>
       <c r="L75" s="13" t="n">
-        <v>3789142.0</v>
+        <v>2.0363636E7</v>
       </c>
       <c r="M75" s="13" t="n">
-        <v>335858.0</v>
+        <v>2036364.0</v>
       </c>
       <c r="N75" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O75" s="13" t="n">
-        <v>4125000.0</v>
+        <v>2.24E7</v>
       </c>
       <c r="P75" s="6" t="inlineStr">
         <is>
@@ -5261,12 +5253,12 @@
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>6638</t>
+          <t>6564</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr">
@@ -5296,16 +5288,16 @@
       </c>
       <c r="K76" s="6"/>
       <c r="L76" s="13" t="n">
-        <v>3.7609091E7</v>
+        <v>1.4706398E7</v>
       </c>
       <c r="M76" s="13" t="n">
-        <v>3760909.0</v>
+        <v>1403602.0</v>
       </c>
       <c r="N76" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O76" s="13" t="n">
-        <v>4.137E7</v>
+        <v>1.611E7</v>
       </c>
       <c r="P76" s="6" t="inlineStr">
         <is>
@@ -5334,12 +5326,12 @@
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>6644</t>
+          <t>6566</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr">
@@ -5369,16 +5361,16 @@
       </c>
       <c r="K77" s="6"/>
       <c r="L77" s="13" t="n">
-        <v>3.2181818E7</v>
+        <v>3789142.0</v>
       </c>
       <c r="M77" s="13" t="n">
-        <v>3218182.0</v>
+        <v>335858.0</v>
       </c>
       <c r="N77" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O77" s="13" t="n">
-        <v>3.54E7</v>
+        <v>4125000.0</v>
       </c>
       <c r="P77" s="6" t="inlineStr">
         <is>
@@ -5407,12 +5399,12 @@
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>6790</t>
+          <t>6638</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr">
@@ -5442,16 +5434,16 @@
       </c>
       <c r="K78" s="6"/>
       <c r="L78" s="13" t="n">
-        <v>1.29545455E8</v>
+        <v>3.7609091E7</v>
       </c>
       <c r="M78" s="13" t="n">
-        <v>1.2954545E7</v>
+        <v>3760909.0</v>
       </c>
       <c r="N78" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O78" s="13" t="n">
-        <v>1.425E8</v>
+        <v>4.137E7</v>
       </c>
       <c r="P78" s="6" t="inlineStr">
         <is>
@@ -5480,12 +5472,12 @@
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>6845</t>
+          <t>6644</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
@@ -5515,16 +5507,16 @@
       </c>
       <c r="K79" s="6"/>
       <c r="L79" s="13" t="n">
-        <v>1.8690909E7</v>
+        <v>3.2181818E7</v>
       </c>
       <c r="M79" s="13" t="n">
-        <v>1869091.0</v>
+        <v>3218182.0</v>
       </c>
       <c r="N79" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O79" s="13" t="n">
-        <v>2.056E7</v>
+        <v>3.54E7</v>
       </c>
       <c r="P79" s="6" t="inlineStr">
         <is>
@@ -5548,32 +5540,32 @@
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>C26MTT</t>
+          <t>C26MTD</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>1389</t>
+          <t>6790</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>3502425499</t>
+          <t>3502344144</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH NPP TOÀN THẮNG PH</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
         </is>
       </c>
       <c r="H80" s="6" t="inlineStr">
         <is>
-          <t>75/9/7 Phạm Hồng Thái, Phường Tam Thắng, Thành Phố Hồ Chí Minh</t>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I80" s="7" t="inlineStr">
@@ -5588,16 +5580,16 @@
       </c>
       <c r="K80" s="6"/>
       <c r="L80" s="13" t="n">
-        <v>4059260.0</v>
+        <v>1.29545455E8</v>
       </c>
       <c r="M80" s="13" t="n">
-        <v>324740.0</v>
+        <v>1.2954545E7</v>
       </c>
       <c r="N80" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O80" s="13" t="n">
-        <v>4384000.0</v>
+        <v>1.425E8</v>
       </c>
       <c r="P80" s="6" t="inlineStr">
         <is>
@@ -5621,32 +5613,32 @@
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>C26MTA</t>
+          <t>C26MTD</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>6845</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>3502426622</t>
+          <t>3502344144</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẢO ANH VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
         </is>
       </c>
       <c r="H81" s="6" t="inlineStr">
         <is>
-          <t>Tổ 12, ấp Phước Hưng, Xã Long Hải, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I81" s="7" t="inlineStr">
@@ -5661,16 +5653,16 @@
       </c>
       <c r="K81" s="6"/>
       <c r="L81" s="13" t="n">
-        <v>2.1348148E7</v>
+        <v>1.8690909E7</v>
       </c>
       <c r="M81" s="13" t="n">
-        <v>1707852.0</v>
+        <v>1869091.0</v>
       </c>
       <c r="N81" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O81" s="13" t="n">
-        <v>2.3056E7</v>
+        <v>2.056E7</v>
       </c>
       <c r="P81" s="6" t="inlineStr">
         <is>
@@ -5694,32 +5686,32 @@
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>C26MYY</t>
+          <t>C26MTT</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>10008</t>
+          <t>1389</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="F82" s="7" t="inlineStr">
         <is>
-          <t>3502474552</t>
+          <t>3502425499</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI TRỌNG GIANG</t>
+          <t>CÔNG TY TNHH NPP TOÀN THẮNG PH</t>
         </is>
       </c>
       <c r="H82" s="6" t="inlineStr">
         <is>
-          <t>B16 Khu Tái Định Cư 199 Lô Khu Nhà Ở Đồi 2, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>75/9/7 Phạm Hồng Thái, Phường Tam Thắng, Thành Phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I82" s="7" t="inlineStr">
@@ -5734,16 +5726,16 @@
       </c>
       <c r="K82" s="6"/>
       <c r="L82" s="13" t="n">
-        <v>2727274.0</v>
+        <v>4059260.0</v>
       </c>
       <c r="M82" s="13" t="n">
-        <v>272727.0</v>
+        <v>324740.0</v>
       </c>
       <c r="N82" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O82" s="13" t="n">
-        <v>3000001.0</v>
+        <v>4384000.0</v>
       </c>
       <c r="P82" s="6" t="inlineStr">
         <is>
@@ -5767,32 +5759,32 @@
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>C26MYY</t>
+          <t>C26MTA</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>9295</t>
+          <t>395</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>3502474552</t>
+          <t>3502426622</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI TRỌNG GIANG</t>
+          <t>CÔNG TY TNHH THẢO ANH VŨNG TÀU</t>
         </is>
       </c>
       <c r="H83" s="6" t="inlineStr">
         <is>
-          <t>B16 Khu Tái Định Cư 199 Lô Khu Nhà Ở Đồi 2, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>Tổ 12, ấp Phước Hưng, Xã Long Hải, TP Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I83" s="7" t="inlineStr">
@@ -5807,16 +5799,16 @@
       </c>
       <c r="K83" s="6"/>
       <c r="L83" s="13" t="n">
-        <v>2727274.0</v>
+        <v>2.1348148E7</v>
       </c>
       <c r="M83" s="13" t="n">
-        <v>272727.0</v>
+        <v>1707852.0</v>
       </c>
       <c r="N83" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O83" s="13" t="n">
-        <v>3000001.0</v>
+        <v>2.3056E7</v>
       </c>
       <c r="P83" s="6" t="inlineStr">
         <is>
@@ -5845,12 +5837,12 @@
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>9324</t>
+          <t>10008</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="F84" s="7" t="inlineStr">
@@ -5918,12 +5910,12 @@
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>9523</t>
+          <t>9295</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="F85" s="7" t="inlineStr">
@@ -5991,27 +5983,27 @@
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>3870</t>
+          <t>9324</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="F86" s="7" t="inlineStr">
         <is>
-          <t>3502483525</t>
+          <t>3502474552</t>
         </is>
       </c>
       <c r="G86" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI ĐẠI Ý 79</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI TRỌNG GIANG</t>
         </is>
       </c>
       <c r="H86" s="6" t="inlineStr">
         <is>
-          <t>Số 22/18/29 đường Nam Kỳ Khởi Nghĩa, Phường Vũng Tàu, TP Hồ Chí Minh , Việt Nam</t>
+          <t>B16 Khu Tái Định Cư 199 Lô Khu Nhà Ở Đồi 2, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I86" s="7" t="inlineStr">
@@ -6021,21 +6013,21 @@
       </c>
       <c r="J86" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K86" s="6"/>
       <c r="L86" s="13" t="n">
-        <v>7.8272727E7</v>
+        <v>2727274.0</v>
       </c>
       <c r="M86" s="13" t="n">
-        <v>7827273.0</v>
+        <v>272727.0</v>
       </c>
       <c r="N86" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O86" s="13" t="n">
-        <v>8.61E7</v>
+        <v>3000001.0</v>
       </c>
       <c r="P86" s="6" t="inlineStr">
         <is>
@@ -6059,32 +6051,32 @@
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>C26MNL</t>
+          <t>C26MYY</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>2509</t>
+          <t>9523</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>3502547930</t>
+          <t>3502474552</t>
         </is>
       </c>
       <c r="G87" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI TRỌNG GIANG</t>
         </is>
       </c>
       <c r="H87" s="6" t="inlineStr">
         <is>
-          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>B16 Khu Tái Định Cư 199 Lô Khu Nhà Ở Đồi 2, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I87" s="7" t="inlineStr">
@@ -6099,16 +6091,16 @@
       </c>
       <c r="K87" s="6"/>
       <c r="L87" s="13" t="n">
-        <v>4.2592593E7</v>
+        <v>2727274.0</v>
       </c>
       <c r="M87" s="13" t="n">
-        <v>3407407.0</v>
+        <v>272727.0</v>
       </c>
       <c r="N87" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O87" s="13" t="n">
-        <v>4.6E7</v>
+        <v>3000001.0</v>
       </c>
       <c r="P87" s="6" t="inlineStr">
         <is>
@@ -6132,32 +6124,32 @@
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>C26MNL</t>
+          <t>C26MYY</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>2515</t>
+          <t>3870</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="F88" s="7" t="inlineStr">
         <is>
-          <t>3502547930</t>
+          <t>3502483525</t>
         </is>
       </c>
       <c r="G88" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI ĐẠI Ý 79</t>
         </is>
       </c>
       <c r="H88" s="6" t="inlineStr">
         <is>
-          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 22/18/29 đường Nam Kỳ Khởi Nghĩa, Phường Vũng Tàu, TP Hồ Chí Minh , Việt Nam</t>
         </is>
       </c>
       <c r="I88" s="7" t="inlineStr">
@@ -6167,21 +6159,21 @@
       </c>
       <c r="J88" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K88" s="6"/>
       <c r="L88" s="13" t="n">
-        <v>1.5185185E7</v>
+        <v>7.8272727E7</v>
       </c>
       <c r="M88" s="13" t="n">
-        <v>1214815.0</v>
+        <v>7827273.0</v>
       </c>
       <c r="N88" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O88" s="13" t="n">
-        <v>1.64E7</v>
+        <v>8.61E7</v>
       </c>
       <c r="P88" s="6" t="inlineStr">
         <is>
@@ -6210,12 +6202,12 @@
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>2549</t>
+          <t>2509</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="F89" s="7" t="inlineStr">
@@ -6245,16 +6237,16 @@
       </c>
       <c r="K89" s="6"/>
       <c r="L89" s="13" t="n">
-        <v>3320000.0</v>
+        <v>4.2592593E7</v>
       </c>
       <c r="M89" s="13" t="n">
-        <v>265600.0</v>
+        <v>3407407.0</v>
       </c>
       <c r="N89" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O89" s="13" t="n">
-        <v>3585600.0</v>
+        <v>4.6E7</v>
       </c>
       <c r="P89" s="6" t="inlineStr">
         <is>
@@ -6283,12 +6275,12 @@
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>2643</t>
+          <t>2515</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="F90" s="7" t="inlineStr">
@@ -6318,16 +6310,16 @@
       </c>
       <c r="K90" s="6"/>
       <c r="L90" s="13" t="n">
-        <v>2.5833333E7</v>
+        <v>1.5185185E7</v>
       </c>
       <c r="M90" s="13" t="n">
-        <v>2066667.0</v>
+        <v>1214815.0</v>
       </c>
       <c r="N90" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O90" s="13" t="n">
-        <v>2.79E7</v>
+        <v>1.64E7</v>
       </c>
       <c r="P90" s="6" t="inlineStr">
         <is>
@@ -6356,12 +6348,12 @@
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>2715</t>
+          <t>2549</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr">
@@ -6391,16 +6383,16 @@
       </c>
       <c r="K91" s="6"/>
       <c r="L91" s="13" t="n">
-        <v>9987037.0</v>
+        <v>3320000.0</v>
       </c>
       <c r="M91" s="13" t="n">
-        <v>798963.0</v>
+        <v>265600.0</v>
       </c>
       <c r="N91" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O91" s="13" t="n">
-        <v>1.0786E7</v>
+        <v>3585600.0</v>
       </c>
       <c r="P91" s="6" t="inlineStr">
         <is>
@@ -6429,12 +6421,12 @@
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>2643</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr">
@@ -6464,16 +6456,16 @@
       </c>
       <c r="K92" s="6"/>
       <c r="L92" s="13" t="n">
-        <v>1425926.0</v>
+        <v>2.5833333E7</v>
       </c>
       <c r="M92" s="13" t="n">
-        <v>114074.0</v>
+        <v>2066667.0</v>
       </c>
       <c r="N92" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O92" s="13" t="n">
-        <v>1540000.0</v>
+        <v>2.79E7</v>
       </c>
       <c r="P92" s="6" t="inlineStr">
         <is>
@@ -6502,12 +6494,12 @@
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>2772</t>
+          <t>2715</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="F93" s="7" t="inlineStr">
@@ -6537,16 +6529,16 @@
       </c>
       <c r="K93" s="6"/>
       <c r="L93" s="13" t="n">
-        <v>3796296.0</v>
+        <v>9987037.0</v>
       </c>
       <c r="M93" s="13" t="n">
-        <v>303704.0</v>
+        <v>798963.0</v>
       </c>
       <c r="N93" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O93" s="13" t="n">
-        <v>4100000.0</v>
+        <v>1.0786E7</v>
       </c>
       <c r="P93" s="6" t="inlineStr">
         <is>
@@ -6575,12 +6567,12 @@
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>2813</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="F94" s="7" t="inlineStr">
@@ -6610,16 +6602,16 @@
       </c>
       <c r="K94" s="6"/>
       <c r="L94" s="13" t="n">
-        <v>2138889.0</v>
+        <v>1425926.0</v>
       </c>
       <c r="M94" s="13" t="n">
-        <v>171111.0</v>
+        <v>114074.0</v>
       </c>
       <c r="N94" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O94" s="13" t="n">
-        <v>2310000.0</v>
+        <v>1540000.0</v>
       </c>
       <c r="P94" s="6" t="inlineStr">
         <is>
@@ -6648,12 +6640,12 @@
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>2909</t>
+          <t>2772</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="F95" s="7" t="inlineStr">
@@ -6683,16 +6675,16 @@
       </c>
       <c r="K95" s="6"/>
       <c r="L95" s="13" t="n">
-        <v>2.8564815E7</v>
+        <v>3796296.0</v>
       </c>
       <c r="M95" s="13" t="n">
-        <v>2285185.0</v>
+        <v>303704.0</v>
       </c>
       <c r="N95" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O95" s="13" t="n">
-        <v>3.085E7</v>
+        <v>4100000.0</v>
       </c>
       <c r="P95" s="6" t="inlineStr">
         <is>
@@ -6711,64 +6703,356 @@
       </c>
       <c r="B96" s="7" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>C26MNL</t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>2813</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t>19/09/2026</t>
+        </is>
+      </c>
+      <c r="F96" s="7" t="inlineStr">
+        <is>
+          <t>3502547930</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+        </is>
+      </c>
+      <c r="H96" s="6" t="inlineStr">
+        <is>
+          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I96" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J96" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K96" s="6"/>
+      <c r="L96" s="13" t="n">
+        <v>2138889.0</v>
+      </c>
+      <c r="M96" s="13" t="n">
+        <v>171111.0</v>
+      </c>
+      <c r="N96" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O96" s="13" t="n">
+        <v>2310000.0</v>
+      </c>
+      <c r="P96" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q96" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="n">
+        <v>91.0</v>
+      </c>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>C26MNL</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>2909</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="F97" s="7" t="inlineStr">
+        <is>
+          <t>3502547930</t>
+        </is>
+      </c>
+      <c r="G97" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+        </is>
+      </c>
+      <c r="H97" s="6" t="inlineStr">
+        <is>
+          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I97" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J97" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K97" s="6"/>
+      <c r="L97" s="13" t="n">
+        <v>2.8564815E7</v>
+      </c>
+      <c r="M97" s="13" t="n">
+        <v>2285185.0</v>
+      </c>
+      <c r="N97" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O97" s="13" t="n">
+        <v>3.085E7</v>
+      </c>
+      <c r="P97" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q97" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="n">
+        <v>92.0</v>
+      </c>
+      <c r="B98" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>C26MNL</t>
+        </is>
+      </c>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>2975</t>
+        </is>
+      </c>
+      <c r="E98" s="7" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="F98" s="7" t="inlineStr">
+        <is>
+          <t>3502547930</t>
+        </is>
+      </c>
+      <c r="G98" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+        </is>
+      </c>
+      <c r="H98" s="6" t="inlineStr">
+        <is>
+          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I98" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J98" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K98" s="6"/>
+      <c r="L98" s="13" t="n">
+        <v>5440000.0</v>
+      </c>
+      <c r="M98" s="13" t="n">
+        <v>435200.0</v>
+      </c>
+      <c r="N98" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O98" s="13" t="n">
+        <v>5875200.0</v>
+      </c>
+      <c r="P98" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q98" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="n">
+        <v>93.0</v>
+      </c>
+      <c r="B99" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>2771</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="F99" s="7" t="inlineStr">
+        <is>
+          <t>3502548042</t>
+        </is>
+      </c>
+      <c r="G99" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH TM DV HỮU TÙNG PHÁT</t>
+        </is>
+      </c>
+      <c r="H99" s="6" t="inlineStr">
+        <is>
+          <t>KHU PHỐ PHƯỚC HƯNG, PHƯỜNG PHÚ MỸ, THÀNH PHỐ HỒ CHÍ MINH</t>
+        </is>
+      </c>
+      <c r="I99" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J99" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K99" s="6"/>
+      <c r="L99" s="13" t="n">
+        <v>1.2190909E7</v>
+      </c>
+      <c r="M99" s="13" t="n">
+        <v>1219091.0</v>
+      </c>
+      <c r="N99" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O99" s="13" t="n">
+        <v>1.341E7</v>
+      </c>
+      <c r="P99" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q99" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="n">
+        <v>94.0</v>
+      </c>
+      <c r="B100" s="7" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C96" s="6" t="inlineStr">
+      <c r="C100" s="6" t="inlineStr">
         <is>
           <t>C26MYX</t>
         </is>
       </c>
-      <c r="D96" s="7" t="inlineStr">
+      <c r="D100" s="7" t="inlineStr">
         <is>
           <t>11088</t>
         </is>
       </c>
-      <c r="E96" s="7" t="inlineStr">
+      <c r="E100" s="7" t="inlineStr">
         <is>
           <t>09/09/2026</t>
         </is>
       </c>
-      <c r="F96" s="7" t="inlineStr">
+      <c r="F100" s="7" t="inlineStr">
         <is>
           <t>3502573440</t>
         </is>
       </c>
-      <c r="G96" s="6" t="inlineStr">
+      <c r="G100" s="6" t="inlineStr">
         <is>
           <t>Trạm Y tế phường Tam Thắng</t>
         </is>
       </c>
-      <c r="H96" s="6" t="inlineStr">
+      <c r="H100" s="6" t="inlineStr">
         <is>
           <t>số 278 Lê Lợi, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
-      <c r="I96" s="7" t="inlineStr">
-        <is>
-          <t>3502550210</t>
-        </is>
-      </c>
-      <c r="J96" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
-        </is>
-      </c>
-      <c r="K96" s="6"/>
-      <c r="L96" s="13"/>
-      <c r="M96" s="13"/>
-      <c r="N96" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O96" s="13" t="n">
+      <c r="I100" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J100" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K100" s="6"/>
+      <c r="L100" s="13"/>
+      <c r="M100" s="13"/>
+      <c r="N100" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O100" s="13" t="n">
         <v>2411000.0</v>
       </c>
-      <c r="P96" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q96" s="6" t="inlineStr">
+      <c r="P100" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q100" s="6" t="inlineStr">
         <is>
           <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
         </is>
